--- a/docs/qa/11Columbus_Q1_nhan-xet.xlsx
+++ b/docs/qa/11Columbus_Q1_nhan-xet.xlsx
@@ -466,7 +466,7 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>Qua kết quả học tập Quý 1, em Dương Phạm Tường Vi đã nắm được phần lớn kiến thức trọng tâm và làm bài khá đều tay. Em đặc biệt vững phần dãy số, làm bài chính xác và trình bày rõ ràng. Điểm số của em cao nhưng số bài tập nộp còn ít, chủ yếu dựa vào các bài kiểm tra; đây là điều em cần khắc phục vì bài tập thường mới rèn được kỹ năng. Sang Quý 2, em nên dành thêm thời gian cho các dạng bài tổng hợp và chủ động hỏi thầy cô ngay khi gặp bài chưa giải được.</v>
+        <v>Trong Quý 1, em Dương Phạm Tường Vi có thái độ học tập tích cực và nắm được phần lớn kiến thức trọng tâm của chương trình. Em đặc biệt vững phần dãy số: các bài làm thể hiện sự chính xác và trình bày rõ ràng, mạch lạc. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, nếu duy trì được sự chuyên cần và mạnh dạn trao đổi với thầy cô khi gặp bài khó, em sẽ tiến bộ rõ rệt.</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -486,7 +486,7 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>Qua kết quả học tập Quý 1, em Đặng Lam Anh đã nắm được phần lớn kiến thức trọng tâm và làm bài khá đều tay. Em đặc biệt vững phần dãy số, làm bài chính xác và trình bày rõ ràng. Em cần san bằng độ chênh giữa các phần, hiện phần phương trình lượng giác còn thấp hơn các phần khác khá rõ. Điểm số của em cao nhưng số bài tập nộp còn ít, chủ yếu dựa vào các bài kiểm tra; đây là điều em cần khắc phục vì bài tập thường mới rèn được kỹ năng. Sang Quý 2, em nên dành thêm thời gian cho các dạng bài tổng hợp và chủ động hỏi thầy cô ngay khi gặp bài chưa giải được.</v>
+        <v>Trong Quý 1, em Đặng Lam Anh có thái độ học tập tích cực và nắm được phần lớn kiến thức trọng tâm của chương trình. Em đặc biệt vững phần dãy số: các bài làm thể hiện sự chính xác và trình bày rõ ràng, mạch lạc. Nếu dành thêm thời gian cho phần phương trình lượng giác, kết quả học tập của em sẽ đồng đều và nổi bật hơn nữa. Bước sang Quý 2, nếu duy trì được sự chuyên cần và mạnh dạn trao đổi với thầy cô khi gặp bài khó, em sẽ tiến bộ rõ rệt.</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -506,7 +506,7 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>Qua kết quả học tập Quý 1, em Đặng Tuệ Minh còn yếu ở nhiều nội dung quan trọng, kết quả chưa phản ánh đúng khả năng của em. Phần cấp số cộng và cấp số nhân là chỗ em yếu nhất, sai chủ yếu do chưa nắm chắc phương pháp chứ không phải do bất cẩn. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, thầy cô sẽ cùng em hệ thống lại kiến thức nền; em cần đi học đều, làm đủ bài tập cơ bản và không ngại hỏi khi chưa hiểu bài.</v>
+        <v>Trong Quý 1, em Đặng Tuệ Minh đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Trong các nội dung của Quý 1, em thể hiện sự cố gắng rõ nhất ở phần đường thẳng, mặt phẳng và quan hệ song song trong không gian. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần cấp số cộng và cấp số nhân trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -526,7 +526,7 @@
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>Qua kết quả học tập Quý 1, em Đinh Bình Minh đã có cố gắng nhưng kiến thức còn ở mức trung bình, nhiều dạng bài chưa làm chủ được. Em học tốt nhất ở phần hàm số lượng giác và công thức lượng giác, nắm được cách làm các dạng cơ bản. Phần đường thẳng, mặt phẳng và quan hệ song song trong không gian là chỗ em yếu nhất, sai chủ yếu do chưa nắm chắc phương pháp chứ không phải do bất cẩn. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, em cần làm lại toàn bộ bài tập đã chữa, ghi chép lại các lỗi sai thường gặp và luyện thêm mỗi tuần để bù phần còn hổng.</v>
+        <v>Trong Quý 1, em Đinh Bình Minh đã có nhiều cố gắng và từng bước làm quen với các dạng toán mới của chương trình. Em học tốt phần hàm số lượng giác và công thức lượng giác và đã nắm được phương pháp giải các dạng bài cơ bản ở nội dung này. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần đường thẳng, mặt phẳng và quan hệ song song trong không gian trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -546,7 +546,7 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>Qua kết quả học tập Quý 1, em Đinh Nhật Minh đã có cố gắng nhưng kiến thức còn ở mức trung bình, nhiều dạng bài chưa làm chủ được. Em học tốt nhất ở phần hàm số lượng giác và công thức lượng giác, nắm được cách làm các dạng cơ bản. Phần đường thẳng, mặt phẳng và quan hệ song song trong không gian là chỗ em yếu nhất, sai chủ yếu do chưa nắm chắc phương pháp chứ không phải do bất cẩn. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, em cần làm lại toàn bộ bài tập đã chữa, ghi chép lại các lỗi sai thường gặp và luyện thêm mỗi tuần để bù phần còn hổng.</v>
+        <v>Trong Quý 1, em Đinh Nhật Minh đã có nhiều cố gắng và từng bước làm quen với các dạng toán mới của chương trình. Em học tốt phần hàm số lượng giác và công thức lượng giác và đã nắm được phương pháp giải các dạng bài cơ bản ở nội dung này. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần đường thẳng, mặt phẳng và quan hệ song song trong không gian trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -566,7 +566,7 @@
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>Qua kết quả học tập Quý 1, em Đoàn Thanh Vân còn yếu ở nhiều nội dung quan trọng, kết quả chưa phản ánh đúng khả năng của em. So với các phần khác, em đỡ vướng nhất ở phần hàm số lượng giác và công thức lượng giác. Phần đường thẳng, mặt phẳng và quan hệ song song trong không gian là chỗ em yếu nhất, sai chủ yếu do chưa nắm chắc phương pháp chứ không phải do bất cẩn. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, thầy cô sẽ cùng em hệ thống lại kiến thức nền; em cần đi học đều, làm đủ bài tập cơ bản và không ngại hỏi khi chưa hiểu bài.</v>
+        <v>Trong Quý 1, em Đoàn Thanh Vân đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Em tiếp thu tốt nhất ở phần hàm số lượng giác và công thức lượng giác, đây là nền tảng thuận lợi để em phát triển thêm. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần đường thẳng, mặt phẳng và quan hệ song song trong không gian trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -586,7 +586,7 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>Qua kết quả học tập Quý 1, em Đỗ Hải Phong đã có cố gắng nhưng kiến thức còn ở mức trung bình, nhiều dạng bài chưa làm chủ được. Em học tốt nhất ở phần dãy số, nắm được cách làm các dạng cơ bản. Phần phương trình lượng giác là chỗ em yếu nhất, sai chủ yếu do chưa nắm chắc phương pháp chứ không phải do bất cẩn. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, em cần làm lại toàn bộ bài tập đã chữa, ghi chép lại các lỗi sai thường gặp và luyện thêm mỗi tuần để bù phần còn hổng.</v>
+        <v>Trong Quý 1, em Đỗ Hải Phong đã có nhiều cố gắng và từng bước làm quen với các dạng toán mới của chương trình. Em học tốt phần dãy số và đã nắm được phương pháp giải các dạng bài cơ bản ở nội dung này. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần phương trình lượng giác trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -606,7 +606,7 @@
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>Qua kết quả học tập Quý 1, em Hoàng Lâm đã có cố gắng nhưng kiến thức còn ở mức trung bình, nhiều dạng bài chưa làm chủ được. Em học tốt nhất ở phần dãy số, nắm được cách làm các dạng cơ bản. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, em cần làm lại toàn bộ bài tập đã chữa, ghi chép lại các lỗi sai thường gặp và luyện thêm mỗi tuần để bù phần còn hổng.</v>
+        <v>Trong Quý 1, em Hoàng Lâm đã có nhiều cố gắng và từng bước làm quen với các dạng toán mới của chương trình. Em học tốt phần dãy số và đã nắm được phương pháp giải các dạng bài cơ bản ở nội dung này. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -626,7 +626,7 @@
         <v/>
       </c>
       <c r="E13" t="str">
-        <v>Qua kết quả học tập Quý 1, em Hồ Anh Phong nắm kiến thức Toán chắc và vận dụng tốt, xứng đáng ở nhóm dẫn đầu lớp. Em đặc biệt vững phần hàm số lượng giác và công thức lượng giác, làm bài chính xác và trình bày rõ ràng. Điểm số của em cao nhưng số bài tập nộp còn ít, chủ yếu dựa vào các bài kiểm tra; đây là điều em cần khắc phục vì bài tập thường mới rèn được kỹ năng. Sang Quý 2, em tiếp tục giữ nhịp học này và thử sức với các bài toán vận dụng cao để chuẩn bị cho kỳ thi học kỳ.</v>
+        <v>Trong Quý 1, em Hồ Anh Phong thể hiện nền tảng kiến thức Toán vững và khả năng vận dụng tốt, kết quả học tập thuộc nhóm cao của lớp. Em đặc biệt vững phần hàm số lượng giác và công thức lượng giác: các bài làm thể hiện sự chính xác và trình bày rõ ràng, mạch lạc. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, với nền tảng hiện có, em hoàn toàn có thể chinh phục các bài toán vận dụng cao và chuẩn bị tốt cho kỳ thi học kỳ.</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -646,7 +646,7 @@
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>Qua kết quả học tập Quý 1, em Lê Anh Thư đã nắm được phần lớn kiến thức trọng tâm và làm bài khá đều tay. Em học tốt nhất ở phần hàm số lượng giác và công thức lượng giác, nắm được cách làm các dạng cơ bản. Điểm số của em cao nhưng số bài tập nộp còn ít, chủ yếu dựa vào các bài kiểm tra; đây là điều em cần khắc phục vì bài tập thường mới rèn được kỹ năng. Sang Quý 2, em nên dành thêm thời gian cho các dạng bài tổng hợp và chủ động hỏi thầy cô ngay khi gặp bài chưa giải được.</v>
+        <v>Trong Quý 1, em Lê Anh Thư có thái độ học tập tích cực và nắm được phần lớn kiến thức trọng tâm của chương trình. Em học tốt phần hàm số lượng giác và công thức lượng giác và đã nắm được phương pháp giải các dạng bài cơ bản ở nội dung này. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, nếu duy trì được sự chuyên cần và mạnh dạn trao đổi với thầy cô khi gặp bài khó, em sẽ tiến bộ rõ rệt.</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -666,7 +666,7 @@
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>Qua kết quả học tập Quý 1, em Lê Trung Đức còn yếu ở nhiều nội dung quan trọng, kết quả chưa phản ánh đúng khả năng của em. Tuy nhiên phần phương trình lượng giác em còn mất căn bản, cần học lại từ khái niệm trước khi luyện bài tập. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, thầy cô sẽ cùng em hệ thống lại kiến thức nền; em cần đi học đều, làm đủ bài tập cơ bản và không ngại hỏi khi chưa hiểu bài.</v>
+        <v>Trong Quý 1, em Lê Trung Đức đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Trong các nội dung của Quý 1, em thể hiện sự cố gắng rõ nhất ở phần đường thẳng, mặt phẳng và quan hệ song song trong không gian. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần phương trình lượng giác trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -686,7 +686,7 @@
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>Qua kết quả học tập Quý 1, em Nguyễn An Nam đã có cố gắng nhưng kiến thức còn ở mức trung bình, nhiều dạng bài chưa làm chủ được. So với các phần khác, em đỡ vướng nhất ở phần hàm số lượng giác và công thức lượng giác. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, em cần làm lại toàn bộ bài tập đã chữa, ghi chép lại các lỗi sai thường gặp và luyện thêm mỗi tuần để bù phần còn hổng.</v>
+        <v>Trong Quý 1, em Nguyễn An Nam đã có nhiều cố gắng và từng bước làm quen với các dạng toán mới của chương trình. Em tiếp thu tốt nhất ở phần hàm số lượng giác và công thức lượng giác, đây là nền tảng thuận lợi để em phát triển thêm. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -706,7 +706,7 @@
         <v/>
       </c>
       <c r="E17" t="str">
-        <v>Qua kết quả học tập Quý 1, em Nguyễn Duy Tuấn Linh đã có cố gắng nhưng kiến thức còn ở mức trung bình, nhiều dạng bài chưa làm chủ được. So với các phần khác, em đỡ vướng nhất ở phần hàm số lượng giác và công thức lượng giác. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, em cần làm lại toàn bộ bài tập đã chữa, ghi chép lại các lỗi sai thường gặp và luyện thêm mỗi tuần để bù phần còn hổng.</v>
+        <v>Trong Quý 1, em Nguyễn Duy Tuấn Linh đã có nhiều cố gắng và từng bước làm quen với các dạng toán mới của chương trình. Em tiếp thu tốt nhất ở phần hàm số lượng giác và công thức lượng giác, đây là nền tảng thuận lợi để em phát triển thêm. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F17" t="str">
         <v/>
@@ -726,7 +726,7 @@
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>Qua kết quả học tập Quý 1, em Nguyễn Hoàng Bách nắm kiến thức Toán chắc và vận dụng tốt, xứng đáng ở nhóm dẫn đầu lớp. Em đặc biệt vững phần dãy số, làm bài chính xác và trình bày rõ ràng. Em cần san bằng độ chênh giữa các phần, hiện phần đường thẳng, mặt phẳng và quan hệ song song trong không gian còn thấp hơn các phần khác khá rõ. Điểm số của em cao nhưng số bài tập nộp còn ít, chủ yếu dựa vào các bài kiểm tra; đây là điều em cần khắc phục vì bài tập thường mới rèn được kỹ năng. Sang Quý 2, em tiếp tục giữ nhịp học này và thử sức với các bài toán vận dụng cao để chuẩn bị cho kỳ thi học kỳ.</v>
+        <v>Trong Quý 1, em Nguyễn Hoàng Bách thể hiện nền tảng kiến thức Toán vững và khả năng vận dụng tốt, kết quả học tập thuộc nhóm cao của lớp. Em đặc biệt vững phần dãy số: các bài làm thể hiện sự chính xác và trình bày rõ ràng, mạch lạc. Nếu dành thêm thời gian cho phần đường thẳng, mặt phẳng và quan hệ song song trong không gian, kết quả học tập của em sẽ đồng đều và nổi bật hơn nữa. Bước sang Quý 2, với nền tảng hiện có, em hoàn toàn có thể chinh phục các bài toán vận dụng cao và chuẩn bị tốt cho kỳ thi học kỳ.</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -746,7 +746,7 @@
         <v/>
       </c>
       <c r="E19" t="str">
-        <v>Qua kết quả học tập Quý 1, em Nguyễn Lê Gia Phong đã có cố gắng nhưng kiến thức còn ở mức trung bình, nhiều dạng bài chưa làm chủ được. Em học tốt nhất ở phần hàm số lượng giác và công thức lượng giác, nắm được cách làm các dạng cơ bản. Phần đường thẳng, mặt phẳng và quan hệ song song trong không gian là chỗ em yếu nhất, sai chủ yếu do chưa nắm chắc phương pháp chứ không phải do bất cẩn. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, em cần làm lại toàn bộ bài tập đã chữa, ghi chép lại các lỗi sai thường gặp và luyện thêm mỗi tuần để bù phần còn hổng.</v>
+        <v>Trong Quý 1, em Nguyễn Lê Gia Phong đã có nhiều cố gắng và từng bước làm quen với các dạng toán mới của chương trình. Em học tốt phần hàm số lượng giác và công thức lượng giác và đã nắm được phương pháp giải các dạng bài cơ bản ở nội dung này. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần đường thẳng, mặt phẳng và quan hệ song song trong không gian trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -766,7 +766,7 @@
         <v/>
       </c>
       <c r="E20" t="str">
-        <v>Qua kết quả học tập Quý 1, em Nguyễn Mai Phương đã nắm được phần lớn kiến thức trọng tâm và làm bài khá đều tay. Em học tốt nhất ở phần hàm số lượng giác và công thức lượng giác, nắm được cách làm các dạng cơ bản. Điểm số của em cao nhưng số bài tập nộp còn ít, chủ yếu dựa vào các bài kiểm tra; đây là điều em cần khắc phục vì bài tập thường mới rèn được kỹ năng. Sang Quý 2, em nên dành thêm thời gian cho các dạng bài tổng hợp và chủ động hỏi thầy cô ngay khi gặp bài chưa giải được.</v>
+        <v>Trong Quý 1, em Nguyễn Mai Phương có thái độ học tập tích cực và nắm được phần lớn kiến thức trọng tâm của chương trình. Em học tốt phần hàm số lượng giác và công thức lượng giác và đã nắm được phương pháp giải các dạng bài cơ bản ở nội dung này. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, nếu duy trì được sự chuyên cần và mạnh dạn trao đổi với thầy cô khi gặp bài khó, em sẽ tiến bộ rõ rệt.</v>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -786,7 +786,7 @@
         <v/>
       </c>
       <c r="E21" t="str">
-        <v>Qua kết quả học tập Quý 1, em Nguyễn Thế Minh nắm kiến thức Toán chắc và vận dụng tốt, xứng đáng ở nhóm dẫn đầu lớp. Em đặc biệt vững phần hàm số lượng giác và công thức lượng giác, làm bài chính xác và trình bày rõ ràng. Điểm số của em cao nhưng số bài tập nộp còn ít, chủ yếu dựa vào các bài kiểm tra; đây là điều em cần khắc phục vì bài tập thường mới rèn được kỹ năng. Sang Quý 2, em tiếp tục giữ nhịp học này và thử sức với các bài toán vận dụng cao để chuẩn bị cho kỳ thi học kỳ.</v>
+        <v>Trong Quý 1, em Nguyễn Thế Minh thể hiện nền tảng kiến thức Toán vững và khả năng vận dụng tốt, kết quả học tập thuộc nhóm cao của lớp. Em đặc biệt vững phần hàm số lượng giác và công thức lượng giác: các bài làm thể hiện sự chính xác và trình bày rõ ràng, mạch lạc. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, với nền tảng hiện có, em hoàn toàn có thể chinh phục các bài toán vận dụng cao và chuẩn bị tốt cho kỳ thi học kỳ.</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -806,7 +806,7 @@
         <v/>
       </c>
       <c r="E22" t="str">
-        <v>Qua kết quả học tập Quý 1, em Nguyễn Tiến Ích Lâm đã nắm được phần lớn kiến thức trọng tâm và làm bài khá đều tay. Em học tốt nhất ở phần hàm số lượng giác và công thức lượng giác, nắm được cách làm các dạng cơ bản. Điểm số của em cao nhưng số bài tập nộp còn ít, chủ yếu dựa vào các bài kiểm tra; đây là điều em cần khắc phục vì bài tập thường mới rèn được kỹ năng. Sang Quý 2, em nên dành thêm thời gian cho các dạng bài tổng hợp và chủ động hỏi thầy cô ngay khi gặp bài chưa giải được.</v>
+        <v>Trong Quý 1, em Nguyễn Tiến Ích Lâm có thái độ học tập tích cực và nắm được phần lớn kiến thức trọng tâm của chương trình. Em học tốt phần hàm số lượng giác và công thức lượng giác và đã nắm được phương pháp giải các dạng bài cơ bản ở nội dung này. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, nếu duy trì được sự chuyên cần và mạnh dạn trao đổi với thầy cô khi gặp bài khó, em sẽ tiến bộ rõ rệt.</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -826,7 +826,7 @@
         <v/>
       </c>
       <c r="E23" t="str">
-        <v>Qua kết quả học tập Quý 1, em Nguyễn Vũ Hà Thành còn yếu ở nhiều nội dung quan trọng, kết quả chưa phản ánh đúng khả năng của em. Phần đường thẳng, mặt phẳng và quan hệ song song trong không gian là chỗ em yếu nhất, sai chủ yếu do chưa nắm chắc phương pháp chứ không phải do bất cẩn. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, thầy cô sẽ cùng em hệ thống lại kiến thức nền; em cần đi học đều, làm đủ bài tập cơ bản và không ngại hỏi khi chưa hiểu bài.</v>
+        <v>Trong Quý 1, em Nguyễn Vũ Hà Thành đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Trong các nội dung của Quý 1, em thể hiện sự cố gắng rõ nhất ở phần hàm số lượng giác và công thức lượng giác. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần đường thẳng, mặt phẳng và quan hệ song song trong không gian trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F23" t="str">
         <v/>
@@ -846,7 +846,7 @@
         <v/>
       </c>
       <c r="E24" t="str">
-        <v>Qua kết quả học tập Quý 1, em Phạm Đức Cường còn yếu ở nhiều nội dung quan trọng, kết quả chưa phản ánh đúng khả năng của em. So với các phần khác, em đỡ vướng nhất ở phần đường thẳng, mặt phẳng và quan hệ song song trong không gian. Phần phương trình lượng giác là chỗ em yếu nhất, sai chủ yếu do chưa nắm chắc phương pháp chứ không phải do bất cẩn. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, thầy cô sẽ cùng em hệ thống lại kiến thức nền; em cần đi học đều, làm đủ bài tập cơ bản và không ngại hỏi khi chưa hiểu bài.</v>
+        <v>Trong Quý 1, em Phạm Đức Cường đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Em tiếp thu tốt nhất ở phần đường thẳng, mặt phẳng và quan hệ song song trong không gian, đây là nền tảng thuận lợi để em phát triển thêm. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần phương trình lượng giác trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F24" t="str">
         <v/>
@@ -866,7 +866,7 @@
         <v/>
       </c>
       <c r="E25" t="str">
-        <v>Qua kết quả học tập Quý 1, em Trần Đức Khải đã có cố gắng nhưng kiến thức còn ở mức trung bình, nhiều dạng bài chưa làm chủ được. Em học tốt nhất ở phần dãy số, nắm được cách làm các dạng cơ bản. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, em cần làm lại toàn bộ bài tập đã chữa, ghi chép lại các lỗi sai thường gặp và luyện thêm mỗi tuần để bù phần còn hổng.</v>
+        <v>Trong Quý 1, em Trần Đức Khải đã có nhiều cố gắng và từng bước làm quen với các dạng toán mới của chương trình. Em học tốt phần dãy số và đã nắm được phương pháp giải các dạng bài cơ bản ở nội dung này. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F25" t="str">
         <v/>
@@ -886,7 +886,7 @@
         <v/>
       </c>
       <c r="E26" t="str">
-        <v>Qua kết quả học tập Quý 1, em Trần Phúc Minh đã có cố gắng nhưng kiến thức còn ở mức trung bình, nhiều dạng bài chưa làm chủ được. Em đặc biệt vững phần dãy số, làm bài chính xác và trình bày rõ ràng. Phần phương trình lượng giác là chỗ em yếu nhất, sai chủ yếu do chưa nắm chắc phương pháp chứ không phải do bất cẩn. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, em cần làm lại toàn bộ bài tập đã chữa, ghi chép lại các lỗi sai thường gặp và luyện thêm mỗi tuần để bù phần còn hổng.</v>
+        <v>Trong Quý 1, em Trần Phúc Minh đã có nhiều cố gắng và từng bước làm quen với các dạng toán mới của chương trình. Em đặc biệt vững phần dãy số: các bài làm thể hiện sự chính xác và trình bày rõ ràng, mạch lạc. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần phương trình lượng giác trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F26" t="str">
         <v/>
@@ -906,7 +906,7 @@
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>Qua kết quả học tập Quý 1, em Trịnh Trần Chí Thành còn yếu ở nhiều nội dung quan trọng, kết quả chưa phản ánh đúng khả năng của em. So với các phần khác, em đỡ vướng nhất ở phần dãy số. Phần phương trình lượng giác là chỗ em yếu nhất, sai chủ yếu do chưa nắm chắc phương pháp chứ không phải do bất cẩn. Về ý thức, em nộp bài đầy đủ và đúng hạn, đây là nền tảng tốt để tiến bộ tiếp. Sang Quý 2, thầy cô sẽ cùng em hệ thống lại kiến thức nền; em cần đi học đều, làm đủ bài tập cơ bản và không ngại hỏi khi chưa hiểu bài.</v>
+        <v>Trong Quý 1, em Trịnh Trần Chí Thành đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Em tiếp thu tốt nhất ở phần dãy số, đây là nền tảng thuận lợi để em phát triển thêm. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần phương trình lượng giác trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F27" t="str">
         <v/>
@@ -926,7 +926,7 @@
         <v/>
       </c>
       <c r="E28" t="str">
-        <v>Qua kết quả học tập Quý 1, em Trịnh Tường Anh đã có cố gắng nhưng kiến thức còn ở mức trung bình, nhiều dạng bài chưa làm chủ được. So với các phần khác, em đỡ vướng nhất ở phần hàm số lượng giác và công thức lượng giác. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, em cần làm lại toàn bộ bài tập đã chữa, ghi chép lại các lỗi sai thường gặp và luyện thêm mỗi tuần để bù phần còn hổng.</v>
+        <v>Trong Quý 1, em Trịnh Tường Anh đã có nhiều cố gắng và từng bước làm quen với các dạng toán mới của chương trình. Em tiếp thu tốt nhất ở phần hàm số lượng giác và công thức lượng giác, đây là nền tảng thuận lợi để em phát triển thêm. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F28" t="str">
         <v/>
@@ -946,7 +946,7 @@
         <v/>
       </c>
       <c r="E29" t="str">
-        <v>Qua kết quả học tập Quý 1, em Vũ Đặng Minh Khôi đã có cố gắng nhưng kiến thức còn ở mức trung bình, nhiều dạng bài chưa làm chủ được. Em học tốt nhất ở phần dãy số, nắm được cách làm các dạng cơ bản. Phần đường thẳng, mặt phẳng và quan hệ song song trong không gian là chỗ em yếu nhất, sai chủ yếu do chưa nắm chắc phương pháp chứ không phải do bất cẩn. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, em cần làm lại toàn bộ bài tập đã chữa, ghi chép lại các lỗi sai thường gặp và luyện thêm mỗi tuần để bù phần còn hổng.</v>
+        <v>Trong Quý 1, em Vũ Đặng Minh Khôi đã có nhiều cố gắng và từng bước làm quen với các dạng toán mới của chương trình. Em học tốt phần dãy số và đã nắm được phương pháp giải các dạng bài cơ bản ở nội dung này. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần đường thẳng, mặt phẳng và quan hệ song song trong không gian trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F29" t="str">
         <v/>
@@ -966,7 +966,7 @@
         <v/>
       </c>
       <c r="E30" t="str">
-        <v>Qua kết quả học tập Quý 1, em Vũ Minh Ngọc còn yếu ở nhiều nội dung quan trọng, kết quả chưa phản ánh đúng khả năng của em. Phần đường thẳng, mặt phẳng và quan hệ song song trong không gian là chỗ em yếu nhất, sai chủ yếu do chưa nắm chắc phương pháp chứ không phải do bất cẩn. Về ý thức, em còn bỏ nhiều bài tập, đây là nguyên nhân chính khiến kết quả chưa cao. Sang Quý 2, thầy cô sẽ cùng em hệ thống lại kiến thức nền; em cần đi học đều, làm đủ bài tập cơ bản và không ngại hỏi khi chưa hiểu bài.</v>
+        <v>Trong Quý 1, em Vũ Minh Ngọc đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Trong các nội dung của Quý 1, em thể hiện sự cố gắng rõ nhất ở phần hàm số lượng giác và công thức lượng giác. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần đường thẳng, mặt phẳng và quan hệ song song trong không gian trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
       </c>
       <c r="F30" t="str">
         <v/>

--- a/docs/qa/11Columbus_Q1_nhan-xet.xlsx
+++ b/docs/qa/11Columbus_Q1_nhan-xet.xlsx
@@ -466,7 +466,7 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>Trong Quý 1, em Dương Phạm Tường Vi có thái độ học tập tích cực và nắm được phần lớn kiến thức trọng tâm của chương trình. Em đặc biệt vững phần dãy số: các bài làm thể hiện sự chính xác và trình bày rõ ràng, mạch lạc. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, nếu duy trì được sự chuyên cần và mạnh dạn trao đổi với thầy cô khi gặp bài khó, em sẽ tiến bộ rõ rệt.</v>
+        <v>Trong Quý 1, em Dương Phạm Tường Vi có kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em nắm vững và vận dụng tốt nhất nội dung dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -486,7 +486,7 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>Trong Quý 1, em Đặng Lam Anh có thái độ học tập tích cực và nắm được phần lớn kiến thức trọng tâm của chương trình. Em đặc biệt vững phần dãy số: các bài làm thể hiện sự chính xác và trình bày rõ ràng, mạch lạc. Nếu dành thêm thời gian cho phần phương trình lượng giác, kết quả học tập của em sẽ đồng đều và nổi bật hơn nữa. Bước sang Quý 2, nếu duy trì được sự chuyên cần và mạnh dạn trao đổi với thầy cô khi gặp bài khó, em sẽ tiến bộ rõ rệt.</v>
+        <v>Trong Quý 1, em Đặng Lam Anh có kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em nắm vững và vận dụng tốt nhất nội dung dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Nội dung phương trình lượng giác còn thấp hơn các phần khác, cần được chú ý củng cố thêm.</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -506,7 +506,7 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>Trong Quý 1, em Đặng Tuệ Minh đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Trong các nội dung của Quý 1, em thể hiện sự cố gắng rõ nhất ở phần đường thẳng, mặt phẳng và quan hệ song song trong không gian. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần cấp số cộng và cấp số nhân trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Đặng Tuệ Minh đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung cấp số cộng và cấp số nhân cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -526,7 +526,7 @@
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>Trong Quý 1, em Đinh Bình Minh đã có nhiều cố gắng và từng bước làm quen với các dạng toán mới của chương trình. Em học tốt phần hàm số lượng giác và công thức lượng giác và đã nắm được phương pháp giải các dạng bài cơ bản ở nội dung này. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần đường thẳng, mặt phẳng và quan hệ song song trong không gian trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Đinh Bình Minh có kết quả học tập môn Toán ở mức trung bình, đã tiếp thu được các nội dung cơ bản của chương trình. Em nắm tốt nội dung hàm số lượng giác và công thức lượng giác và thực hiện được các dạng bài cơ bản của phần này. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -546,7 +546,7 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>Trong Quý 1, em Đinh Nhật Minh đã có nhiều cố gắng và từng bước làm quen với các dạng toán mới của chương trình. Em học tốt phần hàm số lượng giác và công thức lượng giác và đã nắm được phương pháp giải các dạng bài cơ bản ở nội dung này. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần đường thẳng, mặt phẳng và quan hệ song song trong không gian trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Đinh Nhật Minh có kết quả học tập môn Toán ở mức trung bình, đã tiếp thu được các nội dung cơ bản của chương trình. Em nắm tốt nội dung hàm số lượng giác và công thức lượng giác và thực hiện được các dạng bài cơ bản của phần này. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -566,7 +566,7 @@
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>Trong Quý 1, em Đoàn Thanh Vân đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Em tiếp thu tốt nhất ở phần hàm số lượng giác và công thức lượng giác, đây là nền tảng thuận lợi để em phát triển thêm. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần đường thẳng, mặt phẳng và quan hệ song song trong không gian trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Đoàn Thanh Vân đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Trong các nội dung của quý, em tiếp thu tốt nhất phần hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -586,7 +586,7 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>Trong Quý 1, em Đỗ Hải Phong đã có nhiều cố gắng và từng bước làm quen với các dạng toán mới của chương trình. Em học tốt phần dãy số và đã nắm được phương pháp giải các dạng bài cơ bản ở nội dung này. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần phương trình lượng giác trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Đỗ Hải Phong có kết quả học tập môn Toán ở mức trung bình, đã tiếp thu được các nội dung cơ bản của chương trình. Em nắm tốt nội dung dãy số và thực hiện được các dạng bài cơ bản của phần này. Nội dung phương trình lượng giác cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -606,7 +606,7 @@
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>Trong Quý 1, em Hoàng Lâm đã có nhiều cố gắng và từng bước làm quen với các dạng toán mới của chương trình. Em học tốt phần dãy số và đã nắm được phương pháp giải các dạng bài cơ bản ở nội dung này. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Hoàng Lâm có kết quả học tập môn Toán ở mức trung bình, đã tiếp thu được các nội dung cơ bản của chương trình. Em nắm tốt nội dung dãy số và thực hiện được các dạng bài cơ bản của phần này. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -626,7 +626,7 @@
         <v/>
       </c>
       <c r="E13" t="str">
-        <v>Trong Quý 1, em Hồ Anh Phong thể hiện nền tảng kiến thức Toán vững và khả năng vận dụng tốt, kết quả học tập thuộc nhóm cao của lớp. Em đặc biệt vững phần hàm số lượng giác và công thức lượng giác: các bài làm thể hiện sự chính xác và trình bày rõ ràng, mạch lạc. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, với nền tảng hiện có, em hoàn toàn có thể chinh phục các bài toán vận dụng cao và chuẩn bị tốt cho kỳ thi học kỳ.</v>
+        <v>Trong Quý 1, em Hồ Anh Phong có kết quả học tập môn Toán tốt, nền tảng kiến thức vững và khả năng vận dụng thành thạo các nội dung đã học. Em nắm vững và vận dụng tốt nhất nội dung hàm số lượng giác và công thức lượng giác, bài làm thể hiện sự chính xác và trình bày rõ ràng. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -646,7 +646,7 @@
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>Trong Quý 1, em Lê Anh Thư có thái độ học tập tích cực và nắm được phần lớn kiến thức trọng tâm của chương trình. Em học tốt phần hàm số lượng giác và công thức lượng giác và đã nắm được phương pháp giải các dạng bài cơ bản ở nội dung này. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, nếu duy trì được sự chuyên cần và mạnh dạn trao đổi với thầy cô khi gặp bài khó, em sẽ tiến bộ rõ rệt.</v>
+        <v>Trong Quý 1, em Lê Anh Thư có kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em nắm tốt nội dung hàm số lượng giác và công thức lượng giác và thực hiện được các dạng bài cơ bản của phần này. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -666,7 +666,7 @@
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>Trong Quý 1, em Lê Trung Đức đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Trong các nội dung của Quý 1, em thể hiện sự cố gắng rõ nhất ở phần đường thẳng, mặt phẳng và quan hệ song song trong không gian. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần phương trình lượng giác trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Lê Trung Đức đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung phương trình lượng giác cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -686,7 +686,7 @@
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>Trong Quý 1, em Nguyễn An Nam đã có nhiều cố gắng và từng bước làm quen với các dạng toán mới của chương trình. Em tiếp thu tốt nhất ở phần hàm số lượng giác và công thức lượng giác, đây là nền tảng thuận lợi để em phát triển thêm. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Nguyễn An Nam có kết quả học tập môn Toán ở mức trung bình, đã tiếp thu được các nội dung cơ bản của chương trình. Trong các nội dung của quý, em tiếp thu tốt nhất phần hàm số lượng giác và công thức lượng giác. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -706,7 +706,7 @@
         <v/>
       </c>
       <c r="E17" t="str">
-        <v>Trong Quý 1, em Nguyễn Duy Tuấn Linh đã có nhiều cố gắng và từng bước làm quen với các dạng toán mới của chương trình. Em tiếp thu tốt nhất ở phần hàm số lượng giác và công thức lượng giác, đây là nền tảng thuận lợi để em phát triển thêm. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Nguyễn Duy Tuấn Linh có kết quả học tập môn Toán ở mức trung bình, đã tiếp thu được các nội dung cơ bản của chương trình. Trong các nội dung của quý, em tiếp thu tốt nhất phần hàm số lượng giác và công thức lượng giác. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
       </c>
       <c r="F17" t="str">
         <v/>
@@ -726,7 +726,7 @@
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>Trong Quý 1, em Nguyễn Hoàng Bách thể hiện nền tảng kiến thức Toán vững và khả năng vận dụng tốt, kết quả học tập thuộc nhóm cao của lớp. Em đặc biệt vững phần dãy số: các bài làm thể hiện sự chính xác và trình bày rõ ràng, mạch lạc. Nếu dành thêm thời gian cho phần đường thẳng, mặt phẳng và quan hệ song song trong không gian, kết quả học tập của em sẽ đồng đều và nổi bật hơn nữa. Bước sang Quý 2, với nền tảng hiện có, em hoàn toàn có thể chinh phục các bài toán vận dụng cao và chuẩn bị tốt cho kỳ thi học kỳ.</v>
+        <v>Trong Quý 1, em Nguyễn Hoàng Bách có kết quả học tập môn Toán tốt, nền tảng kiến thức vững và khả năng vận dụng thành thạo các nội dung đã học. Em nắm vững và vận dụng tốt nhất nội dung dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian còn thấp hơn các phần khác, cần được chú ý củng cố thêm.</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -746,7 +746,7 @@
         <v/>
       </c>
       <c r="E19" t="str">
-        <v>Trong Quý 1, em Nguyễn Lê Gia Phong đã có nhiều cố gắng và từng bước làm quen với các dạng toán mới của chương trình. Em học tốt phần hàm số lượng giác và công thức lượng giác và đã nắm được phương pháp giải các dạng bài cơ bản ở nội dung này. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần đường thẳng, mặt phẳng và quan hệ song song trong không gian trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Nguyễn Lê Gia Phong có kết quả học tập môn Toán ở mức trung bình, đã tiếp thu được các nội dung cơ bản của chương trình. Em nắm tốt nội dung hàm số lượng giác và công thức lượng giác và thực hiện được các dạng bài cơ bản của phần này. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -766,7 +766,7 @@
         <v/>
       </c>
       <c r="E20" t="str">
-        <v>Trong Quý 1, em Nguyễn Mai Phương có thái độ học tập tích cực và nắm được phần lớn kiến thức trọng tâm của chương trình. Em học tốt phần hàm số lượng giác và công thức lượng giác và đã nắm được phương pháp giải các dạng bài cơ bản ở nội dung này. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, nếu duy trì được sự chuyên cần và mạnh dạn trao đổi với thầy cô khi gặp bài khó, em sẽ tiến bộ rõ rệt.</v>
+        <v>Trong Quý 1, em Nguyễn Mai Phương có kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em nắm tốt nội dung hàm số lượng giác và công thức lượng giác và thực hiện được các dạng bài cơ bản của phần này. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -786,7 +786,7 @@
         <v/>
       </c>
       <c r="E21" t="str">
-        <v>Trong Quý 1, em Nguyễn Thế Minh thể hiện nền tảng kiến thức Toán vững và khả năng vận dụng tốt, kết quả học tập thuộc nhóm cao của lớp. Em đặc biệt vững phần hàm số lượng giác và công thức lượng giác: các bài làm thể hiện sự chính xác và trình bày rõ ràng, mạch lạc. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, với nền tảng hiện có, em hoàn toàn có thể chinh phục các bài toán vận dụng cao và chuẩn bị tốt cho kỳ thi học kỳ.</v>
+        <v>Trong Quý 1, em Nguyễn Thế Minh có kết quả học tập môn Toán tốt, nền tảng kiến thức vững và khả năng vận dụng thành thạo các nội dung đã học. Em nắm vững và vận dụng tốt nhất nội dung hàm số lượng giác và công thức lượng giác, bài làm thể hiện sự chính xác và trình bày rõ ràng. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -806,7 +806,7 @@
         <v/>
       </c>
       <c r="E22" t="str">
-        <v>Trong Quý 1, em Nguyễn Tiến Ích Lâm có thái độ học tập tích cực và nắm được phần lớn kiến thức trọng tâm của chương trình. Em học tốt phần hàm số lượng giác và công thức lượng giác và đã nắm được phương pháp giải các dạng bài cơ bản ở nội dung này. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, nếu duy trì được sự chuyên cần và mạnh dạn trao đổi với thầy cô khi gặp bài khó, em sẽ tiến bộ rõ rệt.</v>
+        <v>Trong Quý 1, em Nguyễn Tiến Ích Lâm có kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em nắm tốt nội dung hàm số lượng giác và công thức lượng giác và thực hiện được các dạng bài cơ bản của phần này. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -826,7 +826,7 @@
         <v/>
       </c>
       <c r="E23" t="str">
-        <v>Trong Quý 1, em Nguyễn Vũ Hà Thành đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Trong các nội dung của Quý 1, em thể hiện sự cố gắng rõ nhất ở phần hàm số lượng giác và công thức lượng giác. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần đường thẳng, mặt phẳng và quan hệ song song trong không gian trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Nguyễn Vũ Hà Thành đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở nội dung hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
       </c>
       <c r="F23" t="str">
         <v/>
@@ -846,7 +846,7 @@
         <v/>
       </c>
       <c r="E24" t="str">
-        <v>Trong Quý 1, em Phạm Đức Cường đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Em tiếp thu tốt nhất ở phần đường thẳng, mặt phẳng và quan hệ song song trong không gian, đây là nền tảng thuận lợi để em phát triển thêm. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần phương trình lượng giác trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Phạm Đức Cường đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Trong các nội dung của quý, em tiếp thu tốt nhất phần đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung phương trình lượng giác cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
       </c>
       <c r="F24" t="str">
         <v/>
@@ -866,7 +866,7 @@
         <v/>
       </c>
       <c r="E25" t="str">
-        <v>Trong Quý 1, em Trần Đức Khải đã có nhiều cố gắng và từng bước làm quen với các dạng toán mới của chương trình. Em học tốt phần dãy số và đã nắm được phương pháp giải các dạng bài cơ bản ở nội dung này. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Trần Đức Khải có kết quả học tập môn Toán ở mức trung bình, đã tiếp thu được các nội dung cơ bản của chương trình. Em nắm tốt nội dung dãy số và thực hiện được các dạng bài cơ bản của phần này. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
       </c>
       <c r="F25" t="str">
         <v/>
@@ -886,7 +886,7 @@
         <v/>
       </c>
       <c r="E26" t="str">
-        <v>Trong Quý 1, em Trần Phúc Minh đã có nhiều cố gắng và từng bước làm quen với các dạng toán mới của chương trình. Em đặc biệt vững phần dãy số: các bài làm thể hiện sự chính xác và trình bày rõ ràng, mạch lạc. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần phương trình lượng giác trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Trần Phúc Minh có kết quả học tập môn Toán ở mức trung bình, đã tiếp thu được các nội dung cơ bản của chương trình. Em nắm vững và vận dụng tốt nhất nội dung dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Nội dung phương trình lượng giác cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
       </c>
       <c r="F26" t="str">
         <v/>
@@ -906,7 +906,7 @@
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>Trong Quý 1, em Trịnh Trần Chí Thành đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Em tiếp thu tốt nhất ở phần dãy số, đây là nền tảng thuận lợi để em phát triển thêm. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần phương trình lượng giác trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Trịnh Trần Chí Thành đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Trong các nội dung của quý, em tiếp thu tốt nhất phần dãy số. Nội dung phương trình lượng giác cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
       </c>
       <c r="F27" t="str">
         <v/>
@@ -926,7 +926,7 @@
         <v/>
       </c>
       <c r="E28" t="str">
-        <v>Trong Quý 1, em Trịnh Tường Anh đã có nhiều cố gắng và từng bước làm quen với các dạng toán mới của chương trình. Em tiếp thu tốt nhất ở phần hàm số lượng giác và công thức lượng giác, đây là nền tảng thuận lợi để em phát triển thêm. Các nội dung trong quý đều được em tiếp thu tương đối đồng đều, tạo thuận lợi cho việc học tiếp ở Quý 2. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Trịnh Tường Anh có kết quả học tập môn Toán ở mức trung bình, đã tiếp thu được các nội dung cơ bản của chương trình. Trong các nội dung của quý, em tiếp thu tốt nhất phần hàm số lượng giác và công thức lượng giác. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
       </c>
       <c r="F28" t="str">
         <v/>
@@ -946,7 +946,7 @@
         <v/>
       </c>
       <c r="E29" t="str">
-        <v>Trong Quý 1, em Vũ Đặng Minh Khôi đã có nhiều cố gắng và từng bước làm quen với các dạng toán mới của chương trình. Em học tốt phần dãy số và đã nắm được phương pháp giải các dạng bài cơ bản ở nội dung này. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần đường thẳng, mặt phẳng và quan hệ song song trong không gian trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Vũ Đặng Minh Khôi có kết quả học tập môn Toán ở mức trung bình, đã tiếp thu được các nội dung cơ bản của chương trình. Em nắm tốt nội dung dãy số và thực hiện được các dạng bài cơ bản của phần này. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
       </c>
       <c r="F29" t="str">
         <v/>
@@ -966,7 +966,7 @@
         <v/>
       </c>
       <c r="E30" t="str">
-        <v>Trong Quý 1, em Vũ Minh Ngọc đã tham gia học tập và có ý thức tiếp thu bài giảng của thầy cô. Trong các nội dung của Quý 1, em thể hiện sự cố gắng rõ nhất ở phần hàm số lượng giác và công thức lượng giác. Để kết quả được toàn diện hơn, em sẽ được thầy cô đồng hành củng cố thêm phần đường thẳng, mặt phẳng và quan hệ song song trong không gian trong thời gian tới. Bước sang Quý 2, thầy cô tin rằng với sự đồng hành của gia đình và nhà trường, em sẽ từng bước vững vàng hơn và đạt kết quả tốt hơn.</v>
+        <v>Trong Quý 1, em Vũ Minh Ngọc đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở nội dung hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
       </c>
       <c r="F30" t="str">
         <v/>

--- a/docs/qa/11Columbus_Q1_nhan-xet.xlsx
+++ b/docs/qa/11Columbus_Q1_nhan-xet.xlsx
@@ -466,7 +466,7 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>Trong Quý 1, em Dương Phạm Tường Vi có kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em nắm vững và vận dụng tốt nhất nội dung dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
+        <v>Trong Quý 1, em Dương Phạm Tường Vi đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Các nội dung trong chương trình được em tiếp thu đều.</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -486,7 +486,7 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>Trong Quý 1, em Đặng Lam Anh có kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em nắm vững và vận dụng tốt nhất nội dung dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Nội dung phương trình lượng giác còn thấp hơn các phần khác, cần được chú ý củng cố thêm.</v>
+        <v>Trong Quý 1, em Đặng Lam Anh đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Em cần củng cố và rèn luyện thêm ở phương trình lượng giác.</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -506,7 +506,7 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>Trong Quý 1, em Đặng Tuệ Minh đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung cấp số cộng và cấp số nhân cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
+        <v>Trong Quý 1, em Đặng Tuệ Minh đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung cấp số cộng và cấp số nhân cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -526,7 +526,7 @@
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>Trong Quý 1, em Đinh Bình Minh có kết quả học tập môn Toán ở mức trung bình, đã tiếp thu được các nội dung cơ bản của chương trình. Em nắm tốt nội dung hàm số lượng giác và công thức lượng giác và thực hiện được các dạng bài cơ bản của phần này. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
+        <v>Trong Quý 1, em Đinh Bình Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -546,7 +546,7 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>Trong Quý 1, em Đinh Nhật Minh có kết quả học tập môn Toán ở mức trung bình, đã tiếp thu được các nội dung cơ bản của chương trình. Em nắm tốt nội dung hàm số lượng giác và công thức lượng giác và thực hiện được các dạng bài cơ bản của phần này. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
+        <v>Trong Quý 1, em Đinh Nhật Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -566,7 +566,7 @@
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>Trong Quý 1, em Đoàn Thanh Vân đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Trong các nội dung của quý, em tiếp thu tốt nhất phần hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
+        <v>Trong Quý 1, em Đoàn Thanh Vân đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -586,7 +586,7 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>Trong Quý 1, em Đỗ Hải Phong có kết quả học tập môn Toán ở mức trung bình, đã tiếp thu được các nội dung cơ bản của chương trình. Em nắm tốt nội dung dãy số và thực hiện được các dạng bài cơ bản của phần này. Nội dung phương trình lượng giác cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
+        <v>Trong Quý 1, em Đỗ Hải Phong đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Em thực hiện tốt các dạng bài của dãy số. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -606,7 +606,7 @@
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>Trong Quý 1, em Hoàng Lâm có kết quả học tập môn Toán ở mức trung bình, đã tiếp thu được các nội dung cơ bản của chương trình. Em nắm tốt nội dung dãy số và thực hiện được các dạng bài cơ bản của phần này. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
+        <v>Trong Quý 1, em Hoàng Lâm đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Em thực hiện tốt các dạng bài của dãy số. Các nội dung trong chương trình được em tiếp thu đều.</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -626,7 +626,7 @@
         <v/>
       </c>
       <c r="E13" t="str">
-        <v>Trong Quý 1, em Hồ Anh Phong có kết quả học tập môn Toán tốt, nền tảng kiến thức vững và khả năng vận dụng thành thạo các nội dung đã học. Em nắm vững và vận dụng tốt nhất nội dung hàm số lượng giác và công thức lượng giác, bài làm thể hiện sự chính xác và trình bày rõ ràng. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
+        <v>Trong Quý 1, em Hồ Anh Phong đạt kết quả học tập môn Toán tốt, nền tảng kiến thức vững và khả năng vận dụng thành thạo các nội dung đã học. Em vận dụng tốt nhất hàm số lượng giác và công thức lượng giác, bài làm thể hiện sự chính xác và trình bày rõ ràng. Các nội dung trong chương trình được em tiếp thu đều.</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -646,7 +646,7 @@
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>Trong Quý 1, em Lê Anh Thư có kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em nắm tốt nội dung hàm số lượng giác và công thức lượng giác và thực hiện được các dạng bài cơ bản của phần này. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
+        <v>Trong Quý 1, em Lê Anh Thư đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Các nội dung trong chương trình được em tiếp thu đều.</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -666,7 +666,7 @@
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>Trong Quý 1, em Lê Trung Đức đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung phương trình lượng giác cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
+        <v>Trong Quý 1, em Lê Trung Đức đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -686,7 +686,7 @@
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>Trong Quý 1, em Nguyễn An Nam có kết quả học tập môn Toán ở mức trung bình, đã tiếp thu được các nội dung cơ bản của chương trình. Trong các nội dung của quý, em tiếp thu tốt nhất phần hàm số lượng giác và công thức lượng giác. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
+        <v>Trong Quý 1, em Nguyễn An Nam đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác. Các nội dung trong chương trình được em tiếp thu đều.</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -706,7 +706,7 @@
         <v/>
       </c>
       <c r="E17" t="str">
-        <v>Trong Quý 1, em Nguyễn Duy Tuấn Linh có kết quả học tập môn Toán ở mức trung bình, đã tiếp thu được các nội dung cơ bản của chương trình. Trong các nội dung của quý, em tiếp thu tốt nhất phần hàm số lượng giác và công thức lượng giác. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
+        <v>Trong Quý 1, em Nguyễn Duy Tuấn Linh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác. Các nội dung trong chương trình được em tiếp thu đều.</v>
       </c>
       <c r="F17" t="str">
         <v/>
@@ -726,7 +726,7 @@
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>Trong Quý 1, em Nguyễn Hoàng Bách có kết quả học tập môn Toán tốt, nền tảng kiến thức vững và khả năng vận dụng thành thạo các nội dung đã học. Em nắm vững và vận dụng tốt nhất nội dung dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian còn thấp hơn các phần khác, cần được chú ý củng cố thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Hoàng Bách đạt kết quả học tập môn Toán tốt, nền tảng kiến thức vững và khả năng vận dụng thành thạo các nội dung đã học. Em vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Em cần củng cố và rèn luyện thêm ở đường thẳng, mặt phẳng và quan hệ song song trong không gian.</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -746,7 +746,7 @@
         <v/>
       </c>
       <c r="E19" t="str">
-        <v>Trong Quý 1, em Nguyễn Lê Gia Phong có kết quả học tập môn Toán ở mức trung bình, đã tiếp thu được các nội dung cơ bản của chương trình. Em nắm tốt nội dung hàm số lượng giác và công thức lượng giác và thực hiện được các dạng bài cơ bản của phần này. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
+        <v>Trong Quý 1, em Nguyễn Lê Gia Phong đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -766,7 +766,7 @@
         <v/>
       </c>
       <c r="E20" t="str">
-        <v>Trong Quý 1, em Nguyễn Mai Phương có kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em nắm tốt nội dung hàm số lượng giác và công thức lượng giác và thực hiện được các dạng bài cơ bản của phần này. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
+        <v>Trong Quý 1, em Nguyễn Mai Phương đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Các nội dung trong chương trình được em tiếp thu đều.</v>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -786,7 +786,7 @@
         <v/>
       </c>
       <c r="E21" t="str">
-        <v>Trong Quý 1, em Nguyễn Thế Minh có kết quả học tập môn Toán tốt, nền tảng kiến thức vững và khả năng vận dụng thành thạo các nội dung đã học. Em nắm vững và vận dụng tốt nhất nội dung hàm số lượng giác và công thức lượng giác, bài làm thể hiện sự chính xác và trình bày rõ ràng. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
+        <v>Trong Quý 1, em Nguyễn Thế Minh đạt kết quả học tập môn Toán tốt, nền tảng kiến thức vững và khả năng vận dụng thành thạo các nội dung đã học. Em vận dụng tốt nhất hàm số lượng giác và công thức lượng giác, bài làm thể hiện sự chính xác và trình bày rõ ràng. Các nội dung trong chương trình được em tiếp thu đều.</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -806,7 +806,7 @@
         <v/>
       </c>
       <c r="E22" t="str">
-        <v>Trong Quý 1, em Nguyễn Tiến Ích Lâm có kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em nắm tốt nội dung hàm số lượng giác và công thức lượng giác và thực hiện được các dạng bài cơ bản của phần này. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
+        <v>Trong Quý 1, em Nguyễn Tiến Ích Lâm đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Các nội dung trong chương trình được em tiếp thu đều.</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -826,7 +826,7 @@
         <v/>
       </c>
       <c r="E23" t="str">
-        <v>Trong Quý 1, em Nguyễn Vũ Hà Thành đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở nội dung hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
+        <v>Trong Quý 1, em Nguyễn Vũ Hà Thành đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F23" t="str">
         <v/>
@@ -846,7 +846,7 @@
         <v/>
       </c>
       <c r="E24" t="str">
-        <v>Trong Quý 1, em Phạm Đức Cường đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Trong các nội dung của quý, em tiếp thu tốt nhất phần đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung phương trình lượng giác cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
+        <v>Trong Quý 1, em Phạm Đức Cường đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em có kết quả khá nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F24" t="str">
         <v/>
@@ -866,7 +866,7 @@
         <v/>
       </c>
       <c r="E25" t="str">
-        <v>Trong Quý 1, em Trần Đức Khải có kết quả học tập môn Toán ở mức trung bình, đã tiếp thu được các nội dung cơ bản của chương trình. Em nắm tốt nội dung dãy số và thực hiện được các dạng bài cơ bản của phần này. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
+        <v>Trong Quý 1, em Trần Đức Khải đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Em thực hiện tốt các dạng bài của dãy số. Các nội dung trong chương trình được em tiếp thu đều.</v>
       </c>
       <c r="F25" t="str">
         <v/>
@@ -886,7 +886,7 @@
         <v/>
       </c>
       <c r="E26" t="str">
-        <v>Trong Quý 1, em Trần Phúc Minh có kết quả học tập môn Toán ở mức trung bình, đã tiếp thu được các nội dung cơ bản của chương trình. Em nắm vững và vận dụng tốt nhất nội dung dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Nội dung phương trình lượng giác cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
+        <v>Trong Quý 1, em Trần Phúc Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Em vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F26" t="str">
         <v/>
@@ -906,7 +906,7 @@
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>Trong Quý 1, em Trịnh Trần Chí Thành đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Trong các nội dung của quý, em tiếp thu tốt nhất phần dãy số. Nội dung phương trình lượng giác cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
+        <v>Trong Quý 1, em Trịnh Trần Chí Thành đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em có kết quả khá nhất ở dãy số. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F27" t="str">
         <v/>
@@ -926,7 +926,7 @@
         <v/>
       </c>
       <c r="E28" t="str">
-        <v>Trong Quý 1, em Trịnh Tường Anh có kết quả học tập môn Toán ở mức trung bình, đã tiếp thu được các nội dung cơ bản của chương trình. Trong các nội dung của quý, em tiếp thu tốt nhất phần hàm số lượng giác và công thức lượng giác. Các nội dung trong quý được em tiếp thu tương đối đồng đều.</v>
+        <v>Trong Quý 1, em Trịnh Tường Anh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác. Các nội dung trong chương trình được em tiếp thu đều.</v>
       </c>
       <c r="F28" t="str">
         <v/>
@@ -946,7 +946,7 @@
         <v/>
       </c>
       <c r="E29" t="str">
-        <v>Trong Quý 1, em Vũ Đặng Minh Khôi có kết quả học tập môn Toán ở mức trung bình, đã tiếp thu được các nội dung cơ bản của chương trình. Em nắm tốt nội dung dãy số và thực hiện được các dạng bài cơ bản của phần này. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
+        <v>Trong Quý 1, em Vũ Đặng Minh Khôi đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Em thực hiện tốt các dạng bài của dãy số. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F29" t="str">
         <v/>
@@ -966,7 +966,7 @@
         <v/>
       </c>
       <c r="E30" t="str">
-        <v>Trong Quý 1, em Vũ Minh Ngọc đã tham gia học tập và bước đầu tiếp cận các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở nội dung hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố thêm để kết quả học tập của em được đồng đều hơn.</v>
+        <v>Trong Quý 1, em Vũ Minh Ngọc đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F30" t="str">
         <v/>

--- a/docs/qa/11Columbus_Q1_nhan-xet.xlsx
+++ b/docs/qa/11Columbus_Q1_nhan-xet.xlsx
@@ -466,7 +466,7 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>Trong Quý 1, em Dương Phạm Tường Vi đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Các nội dung trong chương trình được em tiếp thu đều.</v>
+        <v>Trong Quý 1, em Dương Phạm Tường Vi đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em nắm vững và vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng.</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -486,7 +486,7 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>Trong Quý 1, em Đặng Lam Anh đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Em cần củng cố và rèn luyện thêm ở phương trình lượng giác.</v>
+        <v>Trong Quý 1, em Đặng Lam Anh đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em nắm vững và vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -506,7 +506,7 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>Trong Quý 1, em Đặng Tuệ Minh đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung cấp số cộng và cấp số nhân cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Đặng Tuệ Minh đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Kết quả các bài cuối quý có phần giảm so với giai đoạn đầu, rất có thể do khối lượng kiến thức tăng nhanh ở giai đoạn ôn thi giữa kì. Em đạt kết quả cao nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung cấp số cộng và cấp số nhân cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -526,7 +526,7 @@
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>Trong Quý 1, em Đinh Bình Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Đinh Bình Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Kết quả của em tương đối đồng đều qua các lần kiểm tra, không có giai đoạn nào sa sút rõ rệt. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -546,7 +546,7 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>Trong Quý 1, em Đinh Nhật Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Đinh Nhật Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Kết quả các bài cuối quý có phần giảm so với giai đoạn đầu, rất có thể do khối lượng kiến thức tăng nhanh ở giai đoạn ôn thi giữa kì. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -566,7 +566,7 @@
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>Trong Quý 1, em Đoàn Thanh Vân đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Đoàn Thanh Vân đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -586,7 +586,7 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>Trong Quý 1, em Đỗ Hải Phong đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Em thực hiện tốt các dạng bài của dãy số. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Đỗ Hải Phong đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Kết quả của em tương đối đồng đều qua các lần kiểm tra, không có giai đoạn nào sa sút rõ rệt. Em thực hiện tốt các dạng bài của dãy số. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -606,7 +606,7 @@
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>Trong Quý 1, em Hoàng Lâm đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Em thực hiện tốt các dạng bài của dãy số. Các nội dung trong chương trình được em tiếp thu đều.</v>
+        <v>Trong Quý 1, em Hoàng Lâm đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em thực hiện tốt các dạng bài của dãy số.</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -626,7 +626,7 @@
         <v/>
       </c>
       <c r="E13" t="str">
-        <v>Trong Quý 1, em Hồ Anh Phong đạt kết quả học tập môn Toán tốt, nền tảng kiến thức vững và khả năng vận dụng thành thạo các nội dung đã học. Em vận dụng tốt nhất hàm số lượng giác và công thức lượng giác, bài làm thể hiện sự chính xác và trình bày rõ ràng. Các nội dung trong chương trình được em tiếp thu đều.</v>
+        <v>Trong Quý 1, em Hồ Anh Phong đạt kết quả học tập môn Toán tốt, thể hiện nền tảng kiến thức vững. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em nắm vững và vận dụng tốt nhất hàm số lượng giác và công thức lượng giác, bài làm thể hiện sự chính xác và trình bày rõ ràng.</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -646,7 +646,7 @@
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>Trong Quý 1, em Lê Anh Thư đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Các nội dung trong chương trình được em tiếp thu đều.</v>
+        <v>Trong Quý 1, em Lê Anh Thư đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -666,7 +666,7 @@
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>Trong Quý 1, em Lê Trung Đức đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Lê Trung Đức đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em đạt kết quả cao nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -686,7 +686,7 @@
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>Trong Quý 1, em Nguyễn An Nam đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác. Các nội dung trong chương trình được em tiếp thu đều.</v>
+        <v>Trong Quý 1, em Nguyễn An Nam đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Điều đáng khen là phong độ của em rất ổn định: kết quả các bài gần như đồng đều trong suốt quý. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -706,7 +706,7 @@
         <v/>
       </c>
       <c r="E17" t="str">
-        <v>Trong Quý 1, em Nguyễn Duy Tuấn Linh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác. Các nội dung trong chương trình được em tiếp thu đều.</v>
+        <v>Trong Quý 1, em Nguyễn Duy Tuấn Linh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F17" t="str">
         <v/>
@@ -726,7 +726,7 @@
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>Trong Quý 1, em Nguyễn Hoàng Bách đạt kết quả học tập môn Toán tốt, nền tảng kiến thức vững và khả năng vận dụng thành thạo các nội dung đã học. Em vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Em cần củng cố và rèn luyện thêm ở đường thẳng, mặt phẳng và quan hệ song song trong không gian.</v>
+        <v>Trong Quý 1, em Nguyễn Hoàng Bách đạt kết quả học tập môn Toán tốt, thể hiện nền tảng kiến thức vững. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em nắm vững và vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -746,7 +746,7 @@
         <v/>
       </c>
       <c r="E19" t="str">
-        <v>Trong Quý 1, em Nguyễn Lê Gia Phong đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Lê Gia Phong đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Kết quả các bài cuối quý có phần giảm so với giai đoạn đầu, rất có thể do khối lượng kiến thức tăng nhanh ở giai đoạn ôn thi giữa kì. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -766,7 +766,7 @@
         <v/>
       </c>
       <c r="E20" t="str">
-        <v>Trong Quý 1, em Nguyễn Mai Phương đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Các nội dung trong chương trình được em tiếp thu đều.</v>
+        <v>Trong Quý 1, em Nguyễn Mai Phương đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Điểm nổi bật là em làm tốt hơn hẳn khi kiểm tra tập trung so với luyện tập thường ngày, cho thấy em có khả năng huy động kiến thức dưới áp lực thời gian. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -786,7 +786,7 @@
         <v/>
       </c>
       <c r="E21" t="str">
-        <v>Trong Quý 1, em Nguyễn Thế Minh đạt kết quả học tập môn Toán tốt, nền tảng kiến thức vững và khả năng vận dụng thành thạo các nội dung đã học. Em vận dụng tốt nhất hàm số lượng giác và công thức lượng giác, bài làm thể hiện sự chính xác và trình bày rõ ràng. Các nội dung trong chương trình được em tiếp thu đều.</v>
+        <v>Trong Quý 1, em Nguyễn Thế Minh đạt kết quả học tập môn Toán tốt, thể hiện nền tảng kiến thức vững. Điều đáng khen là phong độ của em rất ổn định: kết quả các bài gần như đồng đều trong suốt quý. Em nắm vững và vận dụng tốt nhất hàm số lượng giác và công thức lượng giác, bài làm thể hiện sự chính xác và trình bày rõ ràng.</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -806,7 +806,7 @@
         <v/>
       </c>
       <c r="E22" t="str">
-        <v>Trong Quý 1, em Nguyễn Tiến Ích Lâm đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm của chương trình. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Các nội dung trong chương trình được em tiếp thu đều.</v>
+        <v>Trong Quý 1, em Nguyễn Tiến Ích Lâm đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -826,7 +826,7 @@
         <v/>
       </c>
       <c r="E23" t="str">
-        <v>Trong Quý 1, em Nguyễn Vũ Hà Thành đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Vũ Hà Thành đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Điểm nổi bật là phần luyện tập thường ngày của em tốt hơn hẳn khi làm đề kiểm tra, cho thấy em nắm chắc các dạng cơ bản nhưng còn lúng túng khi gặp đề tổng hợp. Em đạt kết quả cao nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F23" t="str">
         <v/>
@@ -846,7 +846,7 @@
         <v/>
       </c>
       <c r="E24" t="str">
-        <v>Trong Quý 1, em Phạm Đức Cường đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em có kết quả khá nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Phạm Đức Cường đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em có kết quả khá nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F24" t="str">
         <v/>
@@ -866,7 +866,7 @@
         <v/>
       </c>
       <c r="E25" t="str">
-        <v>Trong Quý 1, em Trần Đức Khải đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Em thực hiện tốt các dạng bài của dãy số. Các nội dung trong chương trình được em tiếp thu đều.</v>
+        <v>Trong Quý 1, em Trần Đức Khải đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em thực hiện tốt các dạng bài của dãy số.</v>
       </c>
       <c r="F25" t="str">
         <v/>
@@ -886,7 +886,7 @@
         <v/>
       </c>
       <c r="E26" t="str">
-        <v>Trong Quý 1, em Trần Phúc Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Em vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Trần Phúc Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em nắm vững và vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F26" t="str">
         <v/>
@@ -906,7 +906,7 @@
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>Trong Quý 1, em Trịnh Trần Chí Thành đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em có kết quả khá nhất ở dãy số. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Trịnh Trần Chí Thành đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em có kết quả khá nhất ở dãy số. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F27" t="str">
         <v/>
@@ -926,7 +926,7 @@
         <v/>
       </c>
       <c r="E28" t="str">
-        <v>Trong Quý 1, em Trịnh Tường Anh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác. Các nội dung trong chương trình được em tiếp thu đều.</v>
+        <v>Trong Quý 1, em Trịnh Tường Anh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F28" t="str">
         <v/>
@@ -946,7 +946,7 @@
         <v/>
       </c>
       <c r="E29" t="str">
-        <v>Trong Quý 1, em Vũ Đặng Minh Khôi đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Em thực hiện tốt các dạng bài của dãy số. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Vũ Đặng Minh Khôi đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em thực hiện tốt các dạng bài của dãy số. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F29" t="str">
         <v/>
@@ -966,7 +966,7 @@
         <v/>
       </c>
       <c r="E30" t="str">
-        <v>Trong Quý 1, em Vũ Minh Ngọc đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Em đạt kết quả cao nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Vũ Minh Ngọc đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Kết quả của em tương đối đồng đều qua các lần kiểm tra, không có giai đoạn nào sa sút rõ rệt. Em đạt kết quả cao nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F30" t="str">
         <v/>

--- a/docs/qa/11Columbus_Q1_nhan-xet.xlsx
+++ b/docs/qa/11Columbus_Q1_nhan-xet.xlsx
@@ -466,7 +466,7 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>Trong Quý 1, em Dương Phạm Tường Vi đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em nắm vững và vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng.</v>
+        <v>Trong Quý 1, em Dương Phạm Tường Vi đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Điều cần lưu ý là các bài tự luận của em còn thiếu bước lập luận hoặc thiếu kết luận, dù hướng làm đúng. Em nắm vững và vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng.</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -486,7 +486,7 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>Trong Quý 1, em Đặng Lam Anh đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em nắm vững và vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Đặng Lam Anh đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Điều cần lưu ý là các bài tự luận của em còn thiếu bước lập luận hoặc thiếu kết luận, dù hướng làm đúng. Em nắm vững và vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -506,7 +506,7 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>Trong Quý 1, em Đặng Tuệ Minh đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Kết quả các bài cuối quý có phần giảm so với giai đoạn đầu, rất có thể do khối lượng kiến thức tăng nhanh ở giai đoạn ôn thi giữa kì. Em đạt kết quả cao nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung cấp số cộng và cấp số nhân cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Đặng Tuệ Minh đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Khi làm bài, em còn để trống một số câu, phần lớn rơi vào các câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung cấp số cộng và cấp số nhân cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -526,7 +526,7 @@
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>Trong Quý 1, em Đinh Bình Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Kết quả của em tương đối đồng đều qua các lần kiểm tra, không có giai đoạn nào sa sút rõ rệt. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Đinh Bình Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Điều cần lưu ý là các bài tự luận của em còn thiếu bước lập luận hoặc thiếu kết luận, dù hướng làm đúng. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -546,7 +546,7 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>Trong Quý 1, em Đinh Nhật Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Kết quả các bài cuối quý có phần giảm so với giai đoạn đầu, rất có thể do khối lượng kiến thức tăng nhanh ở giai đoạn ôn thi giữa kì. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Đinh Nhật Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Nhiều câu em làm được một phần, cho thấy em đã nắm được hướng giải nhưng chưa hoàn thiện hết các ý. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -566,7 +566,7 @@
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>Trong Quý 1, em Đoàn Thanh Vân đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Đoàn Thanh Vân đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Điều cần lưu ý là các bài tự luận của em còn thiếu bước lập luận hoặc thiếu kết luận, dù hướng làm đúng. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -586,7 +586,7 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>Trong Quý 1, em Đỗ Hải Phong đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Kết quả của em tương đối đồng đều qua các lần kiểm tra, không có giai đoạn nào sa sút rõ rệt. Em thực hiện tốt các dạng bài của dãy số. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Đỗ Hải Phong đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Lỗi của em rải ở nhiều dạng khác nhau chứ không tập trung vào một phần kiến thức nào, cho thấy em cần rà soát kỹ hơn sau mỗi bài làm. Em thực hiện tốt các dạng bài của dãy số. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -606,7 +606,7 @@
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>Trong Quý 1, em Hoàng Lâm đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em thực hiện tốt các dạng bài của dãy số.</v>
+        <v>Trong Quý 1, em Hoàng Lâm đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Điều cần lưu ý là các bài tự luận của em còn thiếu bước lập luận hoặc thiếu kết luận, dù hướng làm đúng. Em thực hiện tốt các dạng bài của dãy số.</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -626,7 +626,7 @@
         <v/>
       </c>
       <c r="E13" t="str">
-        <v>Trong Quý 1, em Hồ Anh Phong đạt kết quả học tập môn Toán tốt, thể hiện nền tảng kiến thức vững. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em nắm vững và vận dụng tốt nhất hàm số lượng giác và công thức lượng giác, bài làm thể hiện sự chính xác và trình bày rõ ràng.</v>
+        <v>Trong Quý 1, em Hồ Anh Phong đạt kết quả học tập môn Toán tốt, thể hiện nền tảng kiến thức vững. Đáng chú ý là phần lớn câu hỏi em đều làm đúng, số câu sai không nhiều và thường chỉ là lỗi nhỏ. Em nắm vững và vận dụng tốt nhất hàm số lượng giác và công thức lượng giác, bài làm thể hiện sự chính xác và trình bày rõ ràng.</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -646,7 +646,7 @@
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>Trong Quý 1, em Lê Anh Thư đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác.</v>
+        <v>Trong Quý 1, em Lê Anh Thư đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Điều cần lưu ý là các bài tự luận của em còn thiếu bước lập luận hoặc thiếu kết luận, dù hướng làm đúng. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -666,7 +666,7 @@
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>Trong Quý 1, em Lê Trung Đức đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em đạt kết quả cao nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Lê Trung Đức đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Khi làm bài, em còn để trống một số câu, phần lớn rơi vào các câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -686,7 +686,7 @@
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>Trong Quý 1, em Nguyễn An Nam đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Điều đáng khen là phong độ của em rất ổn định: kết quả các bài gần như đồng đều trong suốt quý. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác.</v>
+        <v>Trong Quý 1, em Nguyễn An Nam đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Nhiều câu em làm được một phần, cho thấy em đã nắm được hướng giải nhưng chưa hoàn thiện hết các ý. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -706,7 +706,7 @@
         <v/>
       </c>
       <c r="E17" t="str">
-        <v>Trong Quý 1, em Nguyễn Duy Tuấn Linh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác.</v>
+        <v>Trong Quý 1, em Nguyễn Duy Tuấn Linh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Nhiều câu em làm được một phần, cho thấy em đã nắm được hướng giải nhưng chưa hoàn thiện hết các ý. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F17" t="str">
         <v/>
@@ -726,7 +726,7 @@
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>Trong Quý 1, em Nguyễn Hoàng Bách đạt kết quả học tập môn Toán tốt, thể hiện nền tảng kiến thức vững. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em nắm vững và vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Hoàng Bách đạt kết quả học tập môn Toán tốt, thể hiện nền tảng kiến thức vững. Điều cần lưu ý là các bài tự luận của em còn thiếu bước lập luận hoặc thiếu kết luận, dù hướng làm đúng. Em nắm vững và vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -746,7 +746,7 @@
         <v/>
       </c>
       <c r="E19" t="str">
-        <v>Trong Quý 1, em Nguyễn Lê Gia Phong đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Kết quả các bài cuối quý có phần giảm so với giai đoạn đầu, rất có thể do khối lượng kiến thức tăng nhanh ở giai đoạn ôn thi giữa kì. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Lê Gia Phong đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Nhiều câu em làm được một phần, cho thấy em đã nắm được hướng giải nhưng chưa hoàn thiện hết các ý. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -766,7 +766,7 @@
         <v/>
       </c>
       <c r="E20" t="str">
-        <v>Trong Quý 1, em Nguyễn Mai Phương đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Điểm nổi bật là em làm tốt hơn hẳn khi kiểm tra tập trung so với luyện tập thường ngày, cho thấy em có khả năng huy động kiến thức dưới áp lực thời gian. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác.</v>
+        <v>Trong Quý 1, em Nguyễn Mai Phương đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Điều cần lưu ý là các bài tự luận của em còn thiếu bước lập luận hoặc thiếu kết luận, dù hướng làm đúng. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -786,7 +786,7 @@
         <v/>
       </c>
       <c r="E21" t="str">
-        <v>Trong Quý 1, em Nguyễn Thế Minh đạt kết quả học tập môn Toán tốt, thể hiện nền tảng kiến thức vững. Điều đáng khen là phong độ của em rất ổn định: kết quả các bài gần như đồng đều trong suốt quý. Em nắm vững và vận dụng tốt nhất hàm số lượng giác và công thức lượng giác, bài làm thể hiện sự chính xác và trình bày rõ ràng.</v>
+        <v>Trong Quý 1, em Nguyễn Thế Minh đạt kết quả học tập môn Toán tốt, thể hiện nền tảng kiến thức vững. Đáng chú ý là phần lớn câu hỏi em đều làm đúng, số câu sai không nhiều và thường chỉ là lỗi nhỏ. Em nắm vững và vận dụng tốt nhất hàm số lượng giác và công thức lượng giác, bài làm thể hiện sự chính xác và trình bày rõ ràng.</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -806,7 +806,7 @@
         <v/>
       </c>
       <c r="E22" t="str">
-        <v>Trong Quý 1, em Nguyễn Tiến Ích Lâm đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác.</v>
+        <v>Trong Quý 1, em Nguyễn Tiến Ích Lâm đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Điều cần lưu ý là các bài tự luận của em còn thiếu bước lập luận hoặc thiếu kết luận, dù hướng làm đúng. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -826,7 +826,7 @@
         <v/>
       </c>
       <c r="E23" t="str">
-        <v>Trong Quý 1, em Nguyễn Vũ Hà Thành đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Điểm nổi bật là phần luyện tập thường ngày của em tốt hơn hẳn khi làm đề kiểm tra, cho thấy em nắm chắc các dạng cơ bản nhưng còn lúng túng khi gặp đề tổng hợp. Em đạt kết quả cao nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Vũ Hà Thành đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Khi làm bài, em còn để trống một số câu, phần lớn rơi vào các câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F23" t="str">
         <v/>
@@ -846,7 +846,7 @@
         <v/>
       </c>
       <c r="E24" t="str">
-        <v>Trong Quý 1, em Phạm Đức Cường đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em có kết quả khá nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Phạm Đức Cường đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Điều cần lưu ý là các bài tự luận của em còn thiếu bước lập luận hoặc thiếu kết luận, dù hướng làm đúng. Em có kết quả khá nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F24" t="str">
         <v/>
@@ -866,7 +866,7 @@
         <v/>
       </c>
       <c r="E25" t="str">
-        <v>Trong Quý 1, em Trần Đức Khải đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em thực hiện tốt các dạng bài của dãy số.</v>
+        <v>Trong Quý 1, em Trần Đức Khải đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Điều cần lưu ý là các bài tự luận của em còn thiếu bước lập luận hoặc thiếu kết luận, dù hướng làm đúng. Em thực hiện tốt các dạng bài của dãy số.</v>
       </c>
       <c r="F25" t="str">
         <v/>
@@ -886,7 +886,7 @@
         <v/>
       </c>
       <c r="E26" t="str">
-        <v>Trong Quý 1, em Trần Phúc Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em nắm vững và vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Trần Phúc Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Khi làm bài, em còn để trống một số câu, phần lớn rơi vào các câu khó hoặc câu cuối đề. Em nắm vững và vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F26" t="str">
         <v/>
@@ -906,7 +906,7 @@
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>Trong Quý 1, em Trịnh Trần Chí Thành đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em có kết quả khá nhất ở dãy số. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Trịnh Trần Chí Thành đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Khi làm bài, em còn để trống một số câu, phần lớn rơi vào các câu khó hoặc câu cuối đề. Em có kết quả khá nhất ở dãy số. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F27" t="str">
         <v/>
@@ -926,7 +926,7 @@
         <v/>
       </c>
       <c r="E28" t="str">
-        <v>Trong Quý 1, em Trịnh Tường Anh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác.</v>
+        <v>Trong Quý 1, em Trịnh Tường Anh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Phần lớn lỗi của em nằm ở bước tính toán, trong khi hướng giải vẫn đúng. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F28" t="str">
         <v/>
@@ -946,7 +946,7 @@
         <v/>
       </c>
       <c r="E29" t="str">
-        <v>Trong Quý 1, em Vũ Đặng Minh Khôi đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Điểm đáng ghi nhận là em có tiến bộ rõ rệt về sau: kết quả những bài cuối quý cao hơn hẳn giai đoạn đầu, cho thấy em đã điều chỉnh được cách học. Em thực hiện tốt các dạng bài của dãy số. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Vũ Đặng Minh Khôi đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Nhiều câu em làm được một phần, cho thấy em đã nắm được hướng giải nhưng chưa hoàn thiện hết các ý. Em thực hiện tốt các dạng bài của dãy số. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F29" t="str">
         <v/>
@@ -966,7 +966,7 @@
         <v/>
       </c>
       <c r="E30" t="str">
-        <v>Trong Quý 1, em Vũ Minh Ngọc đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Kết quả của em tương đối đồng đều qua các lần kiểm tra, không có giai đoạn nào sa sút rõ rệt. Em đạt kết quả cao nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Vũ Minh Ngọc đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Khi làm bài, em còn để trống một số câu, phần lớn rơi vào các câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F30" t="str">
         <v/>

--- a/docs/qa/11Columbus_Q1_nhan-xet.xlsx
+++ b/docs/qa/11Columbus_Q1_nhan-xet.xlsx
@@ -466,7 +466,7 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>Trong Quý 1, em Dương Phạm Tường Vi đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Điều cần lưu ý là các bài tự luận của em còn thiếu bước lập luận hoặc thiếu kết luận, dù hướng làm đúng. Em nắm vững và vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng.</v>
+        <v>Trong Quý 1, em Dương Phạm Tường Vi đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em nắm vững và vận dụng tốt nhất dãy số, bài thi thể hiện sự chính xác và trình bày rõ ràng.</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -486,7 +486,7 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>Trong Quý 1, em Đặng Lam Anh đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Điều cần lưu ý là các bài tự luận của em còn thiếu bước lập luận hoặc thiếu kết luận, dù hướng làm đúng. Em nắm vững và vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Đặng Lam Anh đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em nắm vững và vận dụng tốt nhất dãy số, bài thi thể hiện sự chính xác và trình bày rõ ràng. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -506,7 +506,7 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>Trong Quý 1, em Đặng Tuệ Minh đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Khi làm bài, em còn để trống một số câu, phần lớn rơi vào các câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung cấp số cộng và cấp số nhân cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Đặng Tuệ Minh đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung cấp số cộng và cấp số nhân cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -526,7 +526,7 @@
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>Trong Quý 1, em Đinh Bình Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Điều cần lưu ý là các bài tự luận của em còn thiếu bước lập luận hoặc thiếu kết luận, dù hướng làm đúng. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Đinh Bình Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -546,7 +546,7 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>Trong Quý 1, em Đinh Nhật Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Nhiều câu em làm được một phần, cho thấy em đã nắm được hướng giải nhưng chưa hoàn thiện hết các ý. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Đinh Nhật Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -566,7 +566,7 @@
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>Trong Quý 1, em Đoàn Thanh Vân đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Điều cần lưu ý là các bài tự luận của em còn thiếu bước lập luận hoặc thiếu kết luận, dù hướng làm đúng. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Đoàn Thanh Vân đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -586,7 +586,7 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>Trong Quý 1, em Đỗ Hải Phong đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Lỗi của em rải ở nhiều dạng khác nhau chứ không tập trung vào một phần kiến thức nào, cho thấy em cần rà soát kỹ hơn sau mỗi bài làm. Em thực hiện tốt các dạng bài của dãy số. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Đỗ Hải Phong đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em thực hiện tốt các dạng bài của dãy số. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -606,7 +606,7 @@
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>Trong Quý 1, em Hoàng Lâm đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Điều cần lưu ý là các bài tự luận của em còn thiếu bước lập luận hoặc thiếu kết luận, dù hướng làm đúng. Em thực hiện tốt các dạng bài của dãy số.</v>
+        <v>Trong Quý 1, em Hoàng Lâm đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em thực hiện tốt các dạng bài của dãy số.</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -626,7 +626,7 @@
         <v/>
       </c>
       <c r="E13" t="str">
-        <v>Trong Quý 1, em Hồ Anh Phong đạt kết quả học tập môn Toán tốt, thể hiện nền tảng kiến thức vững. Đáng chú ý là phần lớn câu hỏi em đều làm đúng, số câu sai không nhiều và thường chỉ là lỗi nhỏ. Em nắm vững và vận dụng tốt nhất hàm số lượng giác và công thức lượng giác, bài làm thể hiện sự chính xác và trình bày rõ ràng.</v>
+        <v>Trong Quý 1, em Hồ Anh Phong đạt kết quả học tập môn Toán tốt, thể hiện nền tảng kiến thức vững. Trong quá trình đánh giá, còn nhầm công thức hoặc sai dấu ở một số câu. Em nắm vững và vận dụng tốt nhất hàm số lượng giác và công thức lượng giác, bài thi thể hiện sự chính xác và trình bày rõ ràng.</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -646,7 +646,7 @@
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>Trong Quý 1, em Lê Anh Thư đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Điều cần lưu ý là các bài tự luận của em còn thiếu bước lập luận hoặc thiếu kết luận, dù hướng làm đúng. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác.</v>
+        <v>Trong Quý 1, em Lê Anh Thư đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -666,7 +666,7 @@
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>Trong Quý 1, em Lê Trung Đức đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Khi làm bài, em còn để trống một số câu, phần lớn rơi vào các câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Lê Trung Đức đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -686,7 +686,7 @@
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>Trong Quý 1, em Nguyễn An Nam đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Nhiều câu em làm được một phần, cho thấy em đã nắm được hướng giải nhưng chưa hoàn thiện hết các ý. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác.</v>
+        <v>Trong Quý 1, em Nguyễn An Nam đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -706,7 +706,7 @@
         <v/>
       </c>
       <c r="E17" t="str">
-        <v>Trong Quý 1, em Nguyễn Duy Tuấn Linh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Nhiều câu em làm được một phần, cho thấy em đã nắm được hướng giải nhưng chưa hoàn thiện hết các ý. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác.</v>
+        <v>Trong Quý 1, em Nguyễn Duy Tuấn Linh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Trong quá trình đánh giá, còn vướng ở một số kiến thức nền, cần được củng cố thêm. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F17" t="str">
         <v/>
@@ -726,7 +726,7 @@
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>Trong Quý 1, em Nguyễn Hoàng Bách đạt kết quả học tập môn Toán tốt, thể hiện nền tảng kiến thức vững. Điều cần lưu ý là các bài tự luận của em còn thiếu bước lập luận hoặc thiếu kết luận, dù hướng làm đúng. Em nắm vững và vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Hoàng Bách đạt kết quả học tập môn Toán tốt, thể hiện nền tảng kiến thức vững. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em nắm vững và vận dụng tốt nhất dãy số, bài thi thể hiện sự chính xác và trình bày rõ ràng. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -746,7 +746,7 @@
         <v/>
       </c>
       <c r="E19" t="str">
-        <v>Trong Quý 1, em Nguyễn Lê Gia Phong đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Nhiều câu em làm được một phần, cho thấy em đã nắm được hướng giải nhưng chưa hoàn thiện hết các ý. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Lê Gia Phong đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -766,7 +766,7 @@
         <v/>
       </c>
       <c r="E20" t="str">
-        <v>Trong Quý 1, em Nguyễn Mai Phương đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Điều cần lưu ý là các bài tự luận của em còn thiếu bước lập luận hoặc thiếu kết luận, dù hướng làm đúng. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác.</v>
+        <v>Trong Quý 1, em Nguyễn Mai Phương đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -786,7 +786,7 @@
         <v/>
       </c>
       <c r="E21" t="str">
-        <v>Trong Quý 1, em Nguyễn Thế Minh đạt kết quả học tập môn Toán tốt, thể hiện nền tảng kiến thức vững. Đáng chú ý là phần lớn câu hỏi em đều làm đúng, số câu sai không nhiều và thường chỉ là lỗi nhỏ. Em nắm vững và vận dụng tốt nhất hàm số lượng giác và công thức lượng giác, bài làm thể hiện sự chính xác và trình bày rõ ràng.</v>
+        <v>Trong Quý 1, em Nguyễn Thế Minh đạt kết quả học tập môn Toán tốt, thể hiện nền tảng kiến thức vững. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em nắm vững và vận dụng tốt nhất hàm số lượng giác và công thức lượng giác, bài thi thể hiện sự chính xác và trình bày rõ ràng.</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -806,7 +806,7 @@
         <v/>
       </c>
       <c r="E22" t="str">
-        <v>Trong Quý 1, em Nguyễn Tiến Ích Lâm đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Điều cần lưu ý là các bài tự luận của em còn thiếu bước lập luận hoặc thiếu kết luận, dù hướng làm đúng. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác.</v>
+        <v>Trong Quý 1, em Nguyễn Tiến Ích Lâm đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -826,7 +826,7 @@
         <v/>
       </c>
       <c r="E23" t="str">
-        <v>Trong Quý 1, em Nguyễn Vũ Hà Thành đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Khi làm bài, em còn để trống một số câu, phần lớn rơi vào các câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Vũ Hà Thành đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F23" t="str">
         <v/>
@@ -846,7 +846,7 @@
         <v/>
       </c>
       <c r="E24" t="str">
-        <v>Trong Quý 1, em Phạm Đức Cường đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Điều cần lưu ý là các bài tự luận của em còn thiếu bước lập luận hoặc thiếu kết luận, dù hướng làm đúng. Em có kết quả khá nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Phạm Đức Cường đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em có kết quả khá nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F24" t="str">
         <v/>
@@ -866,7 +866,7 @@
         <v/>
       </c>
       <c r="E25" t="str">
-        <v>Trong Quý 1, em Trần Đức Khải đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Điều cần lưu ý là các bài tự luận của em còn thiếu bước lập luận hoặc thiếu kết luận, dù hướng làm đúng. Em thực hiện tốt các dạng bài của dãy số.</v>
+        <v>Trong Quý 1, em Trần Đức Khải đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em thực hiện tốt các dạng bài của dãy số.</v>
       </c>
       <c r="F25" t="str">
         <v/>
@@ -886,7 +886,7 @@
         <v/>
       </c>
       <c r="E26" t="str">
-        <v>Trong Quý 1, em Trần Phúc Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Khi làm bài, em còn để trống một số câu, phần lớn rơi vào các câu khó hoặc câu cuối đề. Em nắm vững và vận dụng tốt nhất dãy số, bài làm thể hiện sự chính xác và trình bày rõ ràng. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Trần Phúc Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em nắm vững và vận dụng tốt nhất dãy số, bài thi thể hiện sự chính xác và trình bày rõ ràng. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F26" t="str">
         <v/>
@@ -906,7 +906,7 @@
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>Trong Quý 1, em Trịnh Trần Chí Thành đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Khi làm bài, em còn để trống một số câu, phần lớn rơi vào các câu khó hoặc câu cuối đề. Em có kết quả khá nhất ở dãy số. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Trịnh Trần Chí Thành đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em có kết quả khá nhất ở dãy số. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F27" t="str">
         <v/>
@@ -926,7 +926,7 @@
         <v/>
       </c>
       <c r="E28" t="str">
-        <v>Trong Quý 1, em Trịnh Tường Anh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Phần lớn lỗi của em nằm ở bước tính toán, trong khi hướng giải vẫn đúng. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác.</v>
+        <v>Trong Quý 1, em Trịnh Tường Anh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F28" t="str">
         <v/>
@@ -946,7 +946,7 @@
         <v/>
       </c>
       <c r="E29" t="str">
-        <v>Trong Quý 1, em Vũ Đặng Minh Khôi đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Nhiều câu em làm được một phần, cho thấy em đã nắm được hướng giải nhưng chưa hoàn thiện hết các ý. Em thực hiện tốt các dạng bài của dãy số. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Vũ Đặng Minh Khôi đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em thực hiện tốt các dạng bài của dãy số. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F29" t="str">
         <v/>
@@ -966,7 +966,7 @@
         <v/>
       </c>
       <c r="E30" t="str">
-        <v>Trong Quý 1, em Vũ Minh Ngọc đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Khi làm bài, em còn để trống một số câu, phần lớn rơi vào các câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Vũ Minh Ngọc đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F30" t="str">
         <v/>

--- a/docs/qa/11Columbus_Q1_nhan-xet.xlsx
+++ b/docs/qa/11Columbus_Q1_nhan-xet.xlsx
@@ -466,7 +466,7 @@
         <v/>
       </c>
       <c r="E5" t="str">
-        <v>Trong Quý 1, em Dương Phạm Tường Vi đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em nắm vững và vận dụng tốt nhất dãy số, bài thi thể hiện sự chính xác và trình bày rõ ràng.</v>
+        <v>Trong Quý 1, em Dương Phạm Tường Vi đạt kết quả học tập môn Toán ở mức tốt, bài kiểm tra giữa học kì cho thấy nền tảng kiến thức vững và khả năng vận dụng thành thạo. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em nắm vững và vận dụng tốt nhất dãy số, bài thi thể hiện sự chính xác và trình bày rõ ràng.</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -486,7 +486,7 @@
         <v/>
       </c>
       <c r="E6" t="str">
-        <v>Trong Quý 1, em Đặng Lam Anh đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em nắm vững và vận dụng tốt nhất dãy số, bài thi thể hiện sự chính xác và trình bày rõ ràng. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Đặng Lam Anh đạt kết quả học tập môn Toán ở mức khá tốt, nắm chắc các nội dung trọng tâm của chương trình. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em nắm vững và vận dụng tốt nhất dãy số, bài thi thể hiện sự chính xác và trình bày rõ ràng. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -506,7 +506,7 @@
         <v/>
       </c>
       <c r="E7" t="str">
-        <v>Trong Quý 1, em Đặng Tuệ Minh đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung cấp số cộng và cấp số nhân cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Đặng Tuệ Minh bước đầu làm quen với các nội dung của chương trình Toán và đã tham gia đầy đủ các giờ học. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung cấp số cộng và cấp số nhân cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -526,7 +526,7 @@
         <v/>
       </c>
       <c r="E8" t="str">
-        <v>Trong Quý 1, em Đinh Bình Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Đinh Bình Minh đạt kết quả học tập môn Toán ở mức khá, đã nắm được phần lớn kiến thức của chương trình. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -546,7 +546,7 @@
         <v/>
       </c>
       <c r="E9" t="str">
-        <v>Trong Quý 1, em Đinh Nhật Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Đinh Nhật Minh đạt kết quả học tập môn Toán ở mức khá, đã nắm được phần lớn kiến thức của chương trình. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -566,7 +566,7 @@
         <v/>
       </c>
       <c r="E10" t="str">
-        <v>Trong Quý 1, em Đoàn Thanh Vân đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Đoàn Thanh Vân đạt kết quả học tập môn Toán ở mức khá, đã nắm được phần lớn kiến thức của chương trình. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -586,7 +586,7 @@
         <v/>
       </c>
       <c r="E11" t="str">
-        <v>Trong Quý 1, em Đỗ Hải Phong đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em thực hiện tốt các dạng bài của dãy số. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Đỗ Hải Phong đạt kết quả học tập môn Toán ở mức khá, đã nắm được phần lớn kiến thức của chương trình. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em thực hiện tốt các dạng bài của dãy số. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -606,7 +606,7 @@
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>Trong Quý 1, em Hoàng Lâm đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em thực hiện tốt các dạng bài của dãy số.</v>
+        <v>Trong Quý 1, em Hoàng Lâm đạt kết quả học tập môn Toán ở mức khá, đã nắm được phần lớn kiến thức của chương trình. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em thực hiện tốt các dạng bài của dãy số.</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -626,7 +626,7 @@
         <v/>
       </c>
       <c r="E13" t="str">
-        <v>Trong Quý 1, em Hồ Anh Phong đạt kết quả học tập môn Toán tốt, thể hiện nền tảng kiến thức vững. Trong quá trình đánh giá, còn nhầm công thức hoặc sai dấu ở một số câu. Em nắm vững và vận dụng tốt nhất hàm số lượng giác và công thức lượng giác, bài thi thể hiện sự chính xác và trình bày rõ ràng.</v>
+        <v>Trong Quý 1, em Hồ Anh Phong đạt kết quả học tập môn Toán ở mức tốt, bài kiểm tra giữa học kì cho thấy nền tảng kiến thức vững và khả năng vận dụng thành thạo. Trong quá trình đánh giá, còn nhầm công thức hoặc sai dấu ở một số câu. Em nắm vững và vận dụng tốt nhất hàm số lượng giác và công thức lượng giác, bài thi thể hiện sự chính xác và trình bày rõ ràng.</v>
       </c>
       <c r="F13" t="str">
         <v/>
@@ -646,7 +646,7 @@
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>Trong Quý 1, em Lê Anh Thư đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác.</v>
+        <v>Trong Quý 1, em Lê Anh Thư đạt kết quả học tập môn Toán ở mức khá tốt, nắm chắc các nội dung trọng tâm của chương trình. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F14" t="str">
         <v/>
@@ -666,7 +666,7 @@
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>Trong Quý 1, em Lê Trung Đức đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Lê Trung Đức đạt kết quả học tập môn Toán ở mức cơ bản, đã tiếp cận được các kiến thức nền của chương trình. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F15" t="str">
         <v/>
@@ -686,7 +686,7 @@
         <v/>
       </c>
       <c r="E16" t="str">
-        <v>Trong Quý 1, em Nguyễn An Nam đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác.</v>
+        <v>Trong Quý 1, em Nguyễn An Nam đạt kết quả học tập môn Toán ở mức cơ bản, đã tiếp cận được các kiến thức nền của chương trình. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F16" t="str">
         <v/>
@@ -706,7 +706,7 @@
         <v/>
       </c>
       <c r="E17" t="str">
-        <v>Trong Quý 1, em Nguyễn Duy Tuấn Linh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Trong quá trình đánh giá, còn vướng ở một số kiến thức nền, cần được củng cố thêm. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác.</v>
+        <v>Trong Quý 1, em Nguyễn Duy Tuấn Linh đạt kết quả học tập môn Toán ở mức khá, đã nắm được phần lớn kiến thức của chương trình. Trong quá trình đánh giá, còn vướng ở một số kiến thức nền, cần được củng cố thêm. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F17" t="str">
         <v/>
@@ -726,7 +726,7 @@
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>Trong Quý 1, em Nguyễn Hoàng Bách đạt kết quả học tập môn Toán tốt, thể hiện nền tảng kiến thức vững. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em nắm vững và vận dụng tốt nhất dãy số, bài thi thể hiện sự chính xác và trình bày rõ ràng. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Hoàng Bách đạt kết quả học tập môn Toán ở mức tốt, bài kiểm tra giữa học kì cho thấy nền tảng kiến thức vững và khả năng vận dụng thành thạo. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em nắm vững và vận dụng tốt nhất dãy số, bài thi thể hiện sự chính xác và trình bày rõ ràng. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F18" t="str">
         <v/>
@@ -746,7 +746,7 @@
         <v/>
       </c>
       <c r="E19" t="str">
-        <v>Trong Quý 1, em Nguyễn Lê Gia Phong đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Lê Gia Phong đạt kết quả học tập môn Toán ở mức khá tốt, nắm chắc các nội dung trọng tâm của chương trình. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F19" t="str">
         <v/>
@@ -766,7 +766,7 @@
         <v/>
       </c>
       <c r="E20" t="str">
-        <v>Trong Quý 1, em Nguyễn Mai Phương đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác.</v>
+        <v>Trong Quý 1, em Nguyễn Mai Phương đạt kết quả học tập môn Toán ở mức khá tốt, nắm chắc các nội dung trọng tâm của chương trình. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F20" t="str">
         <v/>
@@ -786,7 +786,7 @@
         <v/>
       </c>
       <c r="E21" t="str">
-        <v>Trong Quý 1, em Nguyễn Thế Minh đạt kết quả học tập môn Toán tốt, thể hiện nền tảng kiến thức vững. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em nắm vững và vận dụng tốt nhất hàm số lượng giác và công thức lượng giác, bài thi thể hiện sự chính xác và trình bày rõ ràng.</v>
+        <v>Trong Quý 1, em Nguyễn Thế Minh đạt kết quả học tập môn Toán ở mức tốt, bài kiểm tra giữa học kì cho thấy nền tảng kiến thức vững và khả năng vận dụng thành thạo. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em nắm vững và vận dụng tốt nhất hàm số lượng giác và công thức lượng giác, bài thi thể hiện sự chính xác và trình bày rõ ràng.</v>
       </c>
       <c r="F21" t="str">
         <v/>
@@ -806,7 +806,7 @@
         <v/>
       </c>
       <c r="E22" t="str">
-        <v>Trong Quý 1, em Nguyễn Tiến Ích Lâm đạt kết quả học tập môn Toán ở mức khá, nắm được phần lớn kiến thức trọng tâm. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác.</v>
+        <v>Trong Quý 1, em Nguyễn Tiến Ích Lâm đạt kết quả học tập môn Toán ở mức khá, đã nắm được phần lớn kiến thức của chương trình. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em thực hiện tốt các dạng bài của hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F22" t="str">
         <v/>
@@ -826,7 +826,7 @@
         <v/>
       </c>
       <c r="E23" t="str">
-        <v>Trong Quý 1, em Nguyễn Vũ Hà Thành đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Nguyễn Vũ Hà Thành bước đầu làm quen với các nội dung của chương trình Toán và đã tham gia đầy đủ các giờ học. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F23" t="str">
         <v/>
@@ -846,7 +846,7 @@
         <v/>
       </c>
       <c r="E24" t="str">
-        <v>Trong Quý 1, em Phạm Đức Cường đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em có kết quả khá nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Phạm Đức Cường đạt kết quả học tập môn Toán ở mức khá, đã nắm được phần lớn kiến thức của chương trình. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em có kết quả khá nhất ở đường thẳng, mặt phẳng và quan hệ song song trong không gian. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F24" t="str">
         <v/>
@@ -866,7 +866,7 @@
         <v/>
       </c>
       <c r="E25" t="str">
-        <v>Trong Quý 1, em Trần Đức Khải đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em thực hiện tốt các dạng bài của dãy số.</v>
+        <v>Trong Quý 1, em Trần Đức Khải đạt kết quả học tập môn Toán ở mức khá, đã nắm được phần lớn kiến thức của chương trình. Trong quá trình đánh giá, ở các câu tự luận còn thiếu bước lập luận hoặc chưa có kết luận, dù hướng giải đúng. Em thực hiện tốt các dạng bài của dãy số.</v>
       </c>
       <c r="F25" t="str">
         <v/>
@@ -886,7 +886,7 @@
         <v/>
       </c>
       <c r="E26" t="str">
-        <v>Trong Quý 1, em Trần Phúc Minh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em nắm vững và vận dụng tốt nhất dãy số, bài thi thể hiện sự chính xác và trình bày rõ ràng. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Trần Phúc Minh đạt kết quả học tập môn Toán ở mức tốt, bài kiểm tra giữa học kì cho thấy nền tảng kiến thức vững và khả năng vận dụng thành thạo. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em nắm vững và vận dụng tốt nhất dãy số, bài thi thể hiện sự chính xác và trình bày rõ ràng. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F26" t="str">
         <v/>
@@ -906,7 +906,7 @@
         <v/>
       </c>
       <c r="E27" t="str">
-        <v>Trong Quý 1, em Trịnh Trần Chí Thành đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em có kết quả khá nhất ở dãy số. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Trịnh Trần Chí Thành đạt kết quả học tập môn Toán ở mức cơ bản, đã tiếp cận được các kiến thức nền của chương trình. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em có kết quả khá nhất ở dãy số. Nội dung phương trình lượng giác cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F27" t="str">
         <v/>
@@ -926,7 +926,7 @@
         <v/>
       </c>
       <c r="E28" t="str">
-        <v>Trong Quý 1, em Trịnh Tường Anh đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác.</v>
+        <v>Trong Quý 1, em Trịnh Tường Anh đạt kết quả học tập môn Toán ở mức khá, đã nắm được phần lớn kiến thức của chương trình. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em có kết quả khá nhất ở hàm số lượng giác và công thức lượng giác.</v>
       </c>
       <c r="F28" t="str">
         <v/>
@@ -946,7 +946,7 @@
         <v/>
       </c>
       <c r="E29" t="str">
-        <v>Trong Quý 1, em Vũ Đặng Minh Khôi đạt kết quả học tập môn Toán ở mức trung bình, đã nắm được các kiến thức cơ bản của chương trình. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em thực hiện tốt các dạng bài của dãy số. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Vũ Đặng Minh Khôi đạt kết quả học tập môn Toán ở mức khá, đã nắm được phần lớn kiến thức của chương trình. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em thực hiện tốt các dạng bài của dãy số. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F29" t="str">
         <v/>
@@ -966,7 +966,7 @@
         <v/>
       </c>
       <c r="E30" t="str">
-        <v>Trong Quý 1, em Vũ Minh Ngọc đã tham gia học tập và bước đầu làm quen với các nội dung của chương trình Toán. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
+        <v>Trong Quý 1, em Vũ Minh Ngọc đạt kết quả học tập môn Toán ở mức cơ bản, đã tiếp cận được các kiến thức nền của chương trình. Trong quá trình đánh giá, còn để trống một số câu, phần lớn rơi vào những câu khó hoặc câu cuối đề. Em đạt kết quả cao nhất ở hàm số lượng giác và công thức lượng giác. Nội dung đường thẳng, mặt phẳng và quan hệ song song trong không gian cần được củng cố và rèn luyện thêm.</v>
       </c>
       <c r="F30" t="str">
         <v/>
